--- a/docs/xlsx/jobs-2026-08-18.xlsx
+++ b/docs/xlsx/jobs-2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="1120">
   <si>
     <t>Title</t>
   </si>
@@ -640,15 +640,51 @@
     <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-oakland-california/6395638820</t>
   </si>
   <si>
+    <t>Outbound Sales Representative – Clean Energy</t>
+  </si>
+  <si>
+    <t>Onward Climate</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/outbound-sales-representative/</t>
+  </si>
+  <si>
+    <t>Procurement Intern</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, California, United States</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>20,000 - 40,000</t>
+  </si>
+  <si>
+    <t>Finance / Investing</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/procurement-intern/</t>
+  </si>
+  <si>
     <t>Account Manager, Direct Mail</t>
   </si>
   <si>
     <t>MissionWired</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Full Time</t>
   </si>
   <si>
@@ -661,6 +697,39 @@
     <t>https://www.idealist.org/en/consultant-job/930fa49b26d4498594d8c796b1e022e2-account-manager-direct-mail-missionwired-washington</t>
   </si>
   <si>
+    <t>Adult Family Home Program Manager and Loan Officer</t>
+  </si>
+  <si>
+    <t>Northwest Access Fund</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6a43afe3ade4e33a15362de8573a9bc-adult-family-home-program-manager-and-loan-officer-northwest-access-fund-seattle</t>
+  </si>
+  <si>
+    <t>Advancement Director, Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/808c0400e6d7442bb175c733f3a4a89d-advancement-director-mid-atlantic-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Analista de Marketing Digital</t>
   </si>
   <si>
@@ -697,21 +766,171 @@
     <t>https://www.idealist.org/en/government-job/fd6c6a4d551641c791fed75e917b8613-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
   </si>
   <si>
+    <t>ASSISTANT ATTORNEY GENERAL</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/b706c692fd21470e9cc2e898e3e2b645-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Associate Director, Audience Engagement</t>
+  </si>
+  <si>
+    <t>Human Rights Watch</t>
+  </si>
+  <si>
+    <t>London, England, GB</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/361826f159bb4e468806854d79be4c02-associate-director-audience-engagement-human-rights-watch-london</t>
+  </si>
+  <si>
+    <t>Associate Director, Staff Experience &amp; Special Projects</t>
+  </si>
+  <si>
+    <t>The Hub Project</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b10dbf9d26042c1862a62b7640473e8-associate-director-staff-experience-special-projects-the-hub-project-washington</t>
+  </si>
+  <si>
+    <t>Associate General Counsel for NYS Attorney General (3903)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 91356.00 - 190493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/3ed7127b99c44109bfea58ba0a8ac19d-associate-general-counsel-for-nys-attorney-general-3903-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Attorney - Housing and Communities Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 99437.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/971bd165117f4adea3881194b3d60f13-attorney-housing-and-communities-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney – Client Intake Workgroup</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 103415.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9dc2685a5c64472ba81593b0e705048-attorney-client-intake-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney – Santa Monica Right to Counsel (Stay Housed LA)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 111854.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e7554f434e244ad9e572265a0dd2579-attorney-santa-monica-right-to-counsel-stay-housed-la-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Attorney: Appellate Litigation, OAG’s Criminal Prosecutions (3902)</t>
   </si>
   <si>
-    <t>New York State Office of the Attorney General</t>
-  </si>
-  <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
-    <t>USD 91356.00 - 190493.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/government-job/fd10fa9be79641f88724130093eb7a20-attorney-appellate-litigation-oags-criminal-prosecutions-3902-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Audience Services Manager</t>
+  </si>
+  <si>
+    <t>The Chamber Music Society of Lincoln Center</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/321fcb780705482eafea0f5ae6f50cff-audience-services-manager-the-chamber-music-society-of-lincoln-center-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Program &amp; Partnerships Facilitator (Part-Time)</t>
+  </si>
+  <si>
+    <t>Bilingual Generation</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 85.00/hour</t>
+  </si>
+  <si>
+    <t>Race Ethnicity, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8a3086ab04db4ebc82298bb369540135-bilingual-program-partnerships-facilitator-part-time-bilingual-generation-los-angeles</t>
+  </si>
+  <si>
+    <t>Bilingual Social Worker</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0030f9c086964c5aadcde576e9f08714-bilingual-social-worker-central-union-mission-arlington</t>
+  </si>
+  <si>
+    <t>Canvass Director</t>
+  </si>
+  <si>
+    <t>Meet the Moment NH</t>
+  </si>
+  <si>
+    <t>Manchester, New Hampshire</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fef10221cbc1424faa787091df1e0e1d-canvass-director-meet-the-moment-nh-manchester</t>
+  </si>
+  <si>
     <t>Caregiver &amp; Client Administrative Coordinator</t>
   </si>
   <si>
@@ -730,6 +949,102 @@
     <t>https://www.idealist.org/en/business-job/7a9be35d4efe43e4bdf3730b2bf5d4ba-caregiver-client-administrative-coordinator-chericare-llc-jenkintown</t>
   </si>
   <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>CASA of Placer, Yuba, Sutter</t>
+  </si>
+  <si>
+    <t>Roseville, California</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e188d1f679104147aceaee12a792e171-case-manager-casa-of-placer-yuba-sutter-roseville</t>
+  </si>
+  <si>
+    <t>Case Manager, Snohomish County</t>
+  </si>
+  <si>
+    <t>Anything Helps</t>
+  </si>
+  <si>
+    <t>Lynnwood, Washington</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Crime Safety, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0081e4c631b4626b3a0dd80088245ae-case-manager-snohomish-county-anything-helps-lynnwood</t>
+  </si>
+  <si>
+    <t>Case Worker, Holocaust Survivor Support Services</t>
+  </si>
+  <si>
+    <t>Jewish Community Council of Greater Coney Island</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a4a9aecabaa4e61af436f1abfa11e3c-case-worker-holocaust-survivor-support-services-jewish-community-council-of-greater-coney-island-kings-county</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Wolf Conservation Center</t>
+  </si>
+  <si>
+    <t>South Salem, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8faf817bd68f4af49d2146952ec75377-chief-financial-officer-wolf-conservation-center-south-salem</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Jubilee Housing</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/86879fc0a5764189a84bcee38217a8b7-chief-operating-officer-jubilee-housing-washington</t>
+  </si>
+  <si>
+    <t>Child Abuse Prevention Training Specialist</t>
+  </si>
+  <si>
+    <t>Healing New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d72b2b63a3645e786330d73cc2b78c2-child-abuse-prevention-training-specialist-healing-new-york-new-york</t>
+  </si>
+  <si>
     <t>Civil Rights Attorney</t>
   </si>
   <si>
@@ -748,6 +1063,132 @@
     <t>https://www.idealist.org/en/nonprofit-job/328bae5383c84fb386c3d7b156e46503-civil-rights-attorney-disability-rights-michigan-lansing</t>
   </si>
   <si>
+    <t>Civil Rights Attorney - Bar Association</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1eebe75a3efe46d58433d3d76681f465-civil-rights-attorney-bar-association-disability-rights-michigan-lansing</t>
+  </si>
+  <si>
+    <t>Climate Organizing Director</t>
+  </si>
+  <si>
+    <t>Jobs with Justice San Francisco</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 109500.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Civic Engagement, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91cc49cb41654014b64ccabc8293d839-climate-organizing-director-jobs-with-justice-san-francisco-san-francisco</t>
+  </si>
+  <si>
+    <t>Clinical Manager</t>
+  </si>
+  <si>
+    <t>The North Brooklyn Coalition Against Family Violence</t>
+  </si>
+  <si>
+    <t>Lgbtq, Mental Health, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8a91e7ec55241f0b1a14b63dfd934d6-clinical-manager-the-north-brooklyn-coalition-against-family-violence-new-york</t>
+  </si>
+  <si>
+    <t>Clinical Program Manager, Youth &amp; Family Services</t>
+  </si>
+  <si>
+    <t>Our House NYC Grief Support Center</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56685afabdf84af3a8789434e6fe2202-clinical-program-manager-youth-family-services-our-house-nyc-grief-support-center-new-york</t>
+  </si>
+  <si>
+    <t>Co-Occurring Clinical Team Manager - LICSW LMHC LMFT *$5K Sign On Bonus*</t>
+  </si>
+  <si>
+    <t>Riverside Community Care</t>
+  </si>
+  <si>
+    <t>Milford, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 82750.30 - 82750.30/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e9c8c28af034dda8b7230d059f81a4c-co-occurring-clinical-team-manager-licsw-lmhc-lmft-5k-sign-on-bonus-riverside-community-care-milford</t>
+  </si>
+  <si>
+    <t>Collaboration Experience Manager</t>
+  </si>
+  <si>
+    <t>CAD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/637bc2021e7f49e8a7bcf9acffd6eaed-collaboration-experience-manager-human-rights-watch-new-york</t>
+  </si>
+  <si>
+    <t>Collective Sales Manager</t>
+  </si>
+  <si>
+    <t>Farm Alliance of Baltimore</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77fec11b14254ea7bc22dd645b215bb5-collective-sales-manager-farm-alliance-of-baltimore-baltimore</t>
+  </si>
+  <si>
+    <t>Commmunity Manager</t>
+  </si>
+  <si>
+    <t>DoSomething.org</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 62400.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d2b61700e60451dbd78c8a873747720-commmunity-manager-dosomethingorg-new-york</t>
+  </si>
+  <si>
+    <t>Community Wellness Coordinator</t>
+  </si>
+  <si>
+    <t>Episcopal Community Services</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/77807d583ae8415fabb2f726afe6e3ff-community-wellness-coordinator-episcopal-community-services-philadelphia</t>
+  </si>
+  <si>
     <t>Company Manager/Stage Manager</t>
   </si>
   <si>
@@ -811,6 +1252,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/cf887b8ccc96483883cdb12fe5068287-coordinator-grants-contracts-the-legal-aid-society-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Cross-Cultural HR Professional (Short-Term Mission Assignment)</t>
+  </si>
+  <si>
+    <t>Glory Reborn Organization</t>
+  </si>
+  <si>
+    <t>Cebu City, CEB, PH</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0b23af85ff443b9968cf28576efeaad-cross-cultural-hr-professional-short-term-mission-assignment-glory-reborn-organization-cebu-city</t>
+  </si>
+  <si>
     <t>Data Analyst</t>
   </si>
   <si>
@@ -826,6 +1282,108 @@
     <t>https://www.idealist.org/en/nonprofit-job/4c1a5832912342cf8afc6659777a976b-data-analyst-nami-national-alliance-on-mental-illness-arlington</t>
   </si>
   <si>
+    <t>Data Analyst and Innovation Specialist</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/70f0cab2813543b4aca3ecb8eb04fd2a-data-analyst-and-innovation-specialist-episcopal-community-services-philadelphia</t>
+  </si>
+  <si>
+    <t>Data Analyst/Data Specialist</t>
+  </si>
+  <si>
+    <t>1199 UHE New Organizing Department</t>
+  </si>
+  <si>
+    <t>USD 83809.34 - 83809.34/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f726ebe7175c4f4cb9091897a9af1005-data-analystdata-specialist-1199-uhe-new-organizing-department-new-york</t>
+  </si>
+  <si>
+    <t>Data Associate</t>
+  </si>
+  <si>
+    <t>Afterschool for Children and Teens Now (ACT Now)</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d899c0e9490a4be48c8c2bae897eaf76-data-associate-afterschool-for-children-and-teens-now-act-now-chicago</t>
+  </si>
+  <si>
+    <t>Database Administrator</t>
+  </si>
+  <si>
+    <t>Freshwater Future</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7d89bed31c74ddb8f116501efc7cdc3-database-administrator-freshwater-future-petoskey</t>
+  </si>
+  <si>
+    <t>Day Labor Center Dispatcher (Organizer-in-Training)</t>
+  </si>
+  <si>
+    <t>POMONA ECONOMIC OPPORTUNITY CENTER</t>
+  </si>
+  <si>
+    <t>Pomona, California</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ce632cee17441d8883fc1a69fe190a7-day-labor-center-dispatcher-organizer-in-training-pomona-economic-opportunity-center-pomona</t>
+  </si>
+  <si>
+    <t>Daytime and Overnight House Manager</t>
+  </si>
+  <si>
+    <t>The Gemma Project</t>
+  </si>
+  <si>
+    <t>Antioch, California</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fcbccf7037944aba0739cf869e361fc-daytime-and-overnight-house-manager-the-gemma-project-antioch</t>
+  </si>
+  <si>
+    <t>Deep Canvass Phone Banker</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88c622abc58742d0948a6fae30115587-deep-canvass-phone-banker-addition-indianapolis</t>
+  </si>
+  <si>
     <t>Dental Lab Coordinator</t>
   </si>
   <si>
@@ -856,15 +1414,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/412a4d5d08034412a8f291040ab4f139-development-strategic-partnerships-manager-slice-out-hunger-new-york</t>
   </si>
   <si>
+    <t>Development and Communications Assistant Manager</t>
+  </si>
+  <si>
+    <t>Center for Work Education and Employment</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 62727.00 - 81713.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Education, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29fc77d88e2f43c09b9f90b3f7c2d1f0-development-and-communications-assistant-manager-center-for-work-education-and-employment-denver</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>ADOPT ONE BLOCK</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78678966e8914e60b45e5ac7bba4f032-development-associate-adopt-one-block-portland</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Special Service for Groups, Inc.</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 31.65/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9744ac5701724715b7f4d8e68eefbd88-development-coordinator-special-service-for-groups-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Coordinator- Major Gifts</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0f87e8471d804521b64838ae8adfd107-development-coordinator-major-gifts-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Development Director - Part Time</t>
+  </si>
+  <si>
+    <t>NancyonNorwalk</t>
+  </si>
+  <si>
+    <t>Remote (Connecticut)</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Media, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b24e675564545b7b302205d1a5288e5-development-director-part-time-nancyonnorwalk-norwalk</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
     <t>Suited for Change</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 63000.00 - 68000.00/year</t>
   </si>
   <si>
@@ -874,15 +1510,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/06c4206676c84faabe21aa042e1652c0-development-manager-suited-for-change-washington</t>
   </si>
   <si>
+    <t>The Neighborhood Bridge</t>
+  </si>
+  <si>
+    <t>Oak Park, Illinois</t>
+  </si>
+  <si>
+    <t>USD 67500.00/year</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15ebfbffde6646fcbd2c0ebf74b0844a-development-manager-the-neighborhood-bridge-oak-park</t>
+  </si>
+  <si>
+    <t>Development Manager, Institutional Giving</t>
+  </si>
+  <si>
+    <t>Roderick and Solange MacArthur Justice Center (Chicago)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3eadce3ee5745b59f25856ca9d4f507-development-manager-institutional-giving-roderick-and-solange-macarthur-justice-center-chicago-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5c65fa81e9240f284483c7e09e97efa-development-manager-institutional-giving-roderick-and-solange-macarthur-justice-center-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Development Manager, New York Chapter</t>
+  </si>
+  <si>
+    <t>Remote (Rochester, New York)</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6701982419f4985a9408b33fa0ad6ab-development-manager-new-york-chapter-parkinsons-foundation-rochester</t>
+  </si>
+  <si>
+    <t>Development Operations Associate</t>
+  </si>
+  <si>
+    <t>Giffords: Courage to Fight Gun Violence</t>
+  </si>
+  <si>
+    <t>USD 55880.00 - 59450.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f901ff46f8df4086b9843fb4e531a8fb-development-operations-associate-giffords-courage-to-fight-gun-violence-washington</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
     <t>Brooklyn Boatworks</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 110000.00 - 115000.00/year</t>
   </si>
   <si>
@@ -892,6 +1582,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/ee30dfc65b16498dbbec92a9ea15b941-director-of-development-brooklyn-boatworks-kings-county</t>
   </si>
   <si>
+    <t>Global Village Project</t>
+  </si>
+  <si>
+    <t>Decatur, Georgia</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/979e2c95a0854044a4bc7a5ba7f6fb9c-director-of-development-global-village-project-decatur</t>
+  </si>
+  <si>
     <t>Director of Federal Affairs, Health Care</t>
   </si>
   <si>
@@ -919,9 +1624,6 @@
     <t>Glen Burnie, Maryland</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 60.00/hour</t>
   </si>
   <si>
@@ -931,6 +1633,81 @@
     <t>https://www.idealist.org/en/nonprofit-job/e095bab49707425d8b06d341e6221d3a-director-of-finance-part-time-national-cryptologic-foundation-glen-burnie</t>
   </si>
   <si>
+    <t>Director of Individual Giving &amp; Donor Engagement</t>
+  </si>
+  <si>
+    <t>Asian Americans for Civil Rights and Equality (AACRE)</t>
+  </si>
+  <si>
+    <t>USD 149000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3adac109282b4626a608e59db3ebcfb4-director-of-individual-giving-donor-engagement-asian-americans-for-civil-rights-and-equality-aacre-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Policy and Planning</t>
+  </si>
+  <si>
+    <t>Homeless Services United</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cad06b69295b4521ba6068af4821cc39-director-of-policy-and-planning-homeless-services-united-new-york</t>
+  </si>
+  <si>
+    <t>Director of Stewardship and Asset Management</t>
+  </si>
+  <si>
+    <t>Bay Area Community Land Trust</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a07c212f2b845b79898957b80b2e0bb-director-of-stewardship-and-asset-management-bay-area-community-land-trust-berkeley</t>
+  </si>
+  <si>
+    <t>Director, Access Services, Collection Development &amp; Digital Literacy</t>
+  </si>
+  <si>
+    <t>LA Law Library</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f84e94e0c0694d21a45632736d6ebea0-director-access-services-collection-development-digital-literacy-la-law-library-los-angeles</t>
+  </si>
+  <si>
+    <t>Elementary Special Education Teacher</t>
+  </si>
+  <si>
+    <t>Uncommon Schools</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aafc2b9c93b7442f817b4424145949ed-elementary-special-education-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
     <t>Event Coordinator</t>
   </si>
   <si>
@@ -946,6 +1723,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/be660d6eb2614e8cb2b18edb61fbe3c1-event-coordinator-churches-for-middle-east-peace-washington</t>
   </si>
   <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>EDUCATION THROUGH MUSIC INC</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f785809220fc4c15aa3aad02d8be171b-executive-assistant-education-through-music-inc-new-york</t>
+  </si>
+  <si>
     <t>Executive Coordinator</t>
   </si>
   <si>
@@ -1012,21 +1801,75 @@
     <t>https://www.idealist.org/en/consultant-job/17beee588aed4fb6a89029567d3d26ab-executive-director-latin-american-coalition-armstrong-mcguire-associates-charlotte</t>
   </si>
   <si>
+    <t>Executive Director and Chief Executive Officer (CEO)</t>
+  </si>
+  <si>
+    <t>Tempe Community Council</t>
+  </si>
+  <si>
+    <t>Tempe, Arizona</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02a0bff852a543189b89d6dda924bab0-executive-director-and-chief-executive-officer-ceo-tempe-community-council-tempe</t>
+  </si>
+  <si>
+    <t>Facilities Assistant</t>
+  </si>
+  <si>
+    <t>Center Theatre Group of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2cd1506e41cb472db9a2463fc9e3053e-facilities-assistant-center-theatre-group-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Facilities Manager</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a0fae4ab0b145189a222758d2196977-facilities-manager-center-theatre-group-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Fall 2026 Organizing Fellowship</t>
+  </si>
+  <si>
+    <t>Lead Locally</t>
+  </si>
+  <si>
+    <t>Eugene, Oregon</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88e896930c9040a0a5b384e198d505d9-fall-2026-organizing-fellowship-lead-locally-eugene</t>
+  </si>
+  <si>
     <t>Finance &amp; Operations Manager</t>
   </si>
   <si>
     <t>Future Roots Inc (dublab)</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 31200.00 - 34320.00/year</t>
   </si>
   <si>
-    <t>Arts Music</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/b94ac9f2cd9b44a38f54c13e8d06eaaa-finance-operations-manager-future-roots-inc-dublab-los-angeles</t>
   </si>
   <si>
@@ -1036,18 +1879,39 @@
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 50.00 - 100.00/month</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9bc71568335c45259b22c8b4ddea5020-freelancer-international-fundraiser-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Fundraising and Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>Arlington Sister City Association, Inc.</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59c87ef37a2540f5a256201ffa44d39f-fundraising-and-community-engagement-manager-arlington-sister-city-association-inc-arlington</t>
+  </si>
+  <si>
+    <t>Government Performance Lab Fellow</t>
+  </si>
+  <si>
+    <t>Government Performance Lab</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c30acce8c00141078c66a0efa4e7bba3-government-performance-lab-fellow-government-performance-lab-cambridge</t>
+  </si>
+  <si>
     <t>Grant Writer</t>
   </si>
   <si>
@@ -1066,6 +1930,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/e4ffbab7e18a46b9a529fa18c89b76c9-grant-writer-educational-alliance-new-york</t>
   </si>
   <si>
+    <t>Hellman and Simons Fellow for Science, Engineering, and Technology</t>
+  </si>
+  <si>
+    <t>American Academy of Arts and Sciences</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/889e6cfe814745e7a8a76fc62cf252cd-hellman-and-simons-fellow-for-science-engineering-and-technology-american-academy-of-arts-and-sciences-cambridge</t>
+  </si>
+  <si>
+    <t>High School Special Education Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d54dff2048c0468d87efaaaf1bf55a88-high-school-special-education-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
     <t>Housing Attorney</t>
   </si>
   <si>
@@ -1081,6 +1966,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/643d53ad701744b2866da0a33469319a-housing-attorney-nmic-northern-manhattan-improvement-corporation-new-york</t>
   </si>
   <si>
+    <t>Housing Project Manager</t>
+  </si>
+  <si>
+    <t>Neighborhood Housing Services of New York City</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1bbba99731a489db7d1b79c032511f0-housing-project-manager-neighborhood-housing-services-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Individual and Major Giving Director</t>
+  </si>
+  <si>
+    <t>Encore Community Services</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29eb8f274ee9425c89ec03c57dfa1f39-individual-and-major-giving-director-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>Institutional Giving Manager, George Street Playhouse</t>
+  </si>
+  <si>
+    <t>George Street Playhouse</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/442ce0a6fa0c49c69f596c8e8e79e73f-institutional-giving-manager-george-street-playhouse-george-street-playhouse-new-brunswick</t>
+  </si>
+  <si>
     <t>Interstate Program Coordinator</t>
   </si>
   <si>
@@ -1090,24 +2014,111 @@
     <t>USD 67000.00 - 77000.00/year</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/219cb5c2c1d04fcc882f8dd7e8401e95-interstate-program-coordinator-american-public-human-services-association-arlington</t>
   </si>
   <si>
+    <t>Investigative Analyst: Investigate Police Misconduct (6457)</t>
+  </si>
+  <si>
+    <t>USD 75389.00 - 75389.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/0b360a603a1f44b4858566ceef63971b-investigative-analyst-investigate-police-misconduct-6457-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
     <t>Investigator, Trial Office (Citywide)</t>
   </si>
   <si>
     <t>USD 64207.00 - 92290.00/year</t>
   </si>
   <si>
-    <t>Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/1be7389458ee4f898b3d302c0bcb6b6e-investigator-trial-office-citywide-the-legal-aid-society-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Legal Fellowship</t>
+  </si>
+  <si>
+    <t>Citizens for Responsibility and Ethics in Washington</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40f329c0fa7c489db8418b5bf8c35cac-legal-fellowship-citizens-for-responsibility-and-ethics-in-washington-washington</t>
+  </si>
+  <si>
+    <t>Literacy Specialist</t>
+  </si>
+  <si>
+    <t>Literacy New Jersey</t>
+  </si>
+  <si>
+    <t>Kearny, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 50960.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13408098ff4d40f995f4d2d41c4464ed-literacy-specialist-literacy-new-jersey-kearny</t>
+  </si>
+  <si>
+    <t>Manager, Direct Marketing</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>USD 77600.00 - 107500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0d5192f53854642bb67f1cefee7f183-manager-direct-marketing-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>USD 74400.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84bc4e19db0f4438b605a78844a32380-manager-direct-marketing-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>Managing Attorney - External Partnerships</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>USD 95500.00 - 111500.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a2eb5631c7e4d7898ccdff67f4ba766-managing-attorney-external-partnerships-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Managing Attorney-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>Catholic Charities of Los Angeles, Inc</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 90271.00/year</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e95dbdfa77d4478abee624fb83f20ad-managing-attorney-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
     <t>MANAGING DIRECTOR OF EQUITY, PEOPLE, AND CULTURE at CAL</t>
   </si>
   <si>
@@ -1123,6 +2134,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/d2809961f9b34e71b7430ea1b52e98d8-managing-director-of-equity-people-and-culture-at-cal-center-for-appellate-litigation-new-york</t>
   </si>
   <si>
+    <t>Marketing and Communications Associate</t>
+  </si>
+  <si>
+    <t>The ARK, Inc.</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6288a4a770c44f9e9af00e6ad8930882-marketing-and-communications-associate-the-ark-inc-chicago</t>
+  </si>
+  <si>
+    <t>MCH Data Analyst</t>
+  </si>
+  <si>
+    <t>Mamatoto Village</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Health Medicine, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a96f3444d4474882879686d410865c09-mch-data-analyst-mamatoto-village-washington</t>
+  </si>
+  <si>
     <t>Membership Specialist</t>
   </si>
   <si>
@@ -1138,6 +2176,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/b93e822986e549e4bdf91ed4755a0de1-membership-specialist-the-science-friday-initiative-new-york</t>
   </si>
   <si>
+    <t>Middle School Science Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58c379679dd54b4e827115d951c1eddb-middle-school-science-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
+    <t>Middle School Special Education Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d24dd93ea2974a5499ee15a3a4c60e9c-middle-school-special-education-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
+    <t>NJSACC Seeks Full-Time Quality Specialist, Afterschool &amp; OST</t>
+  </si>
+  <si>
+    <t>NJSACC: New Jersey's Afterschool and Out-of-School Time Professional Network</t>
+  </si>
+  <si>
+    <t>Westfield, NJ</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d91d5392ae9f4dd1b38e6064a5f68136-njsacc-seeks-full-time-quality-specialist-afterschool-ost-njsacc-new-jerseys-afterschool-and-out-of-school-time-professional-network-westfield</t>
+  </si>
+  <si>
     <t>nvestigative Analyst: Investigate Police Misconduct (6456)</t>
   </si>
   <si>
@@ -1156,9 +2221,6 @@
     <t>On Purpose</t>
   </si>
   <si>
-    <t>London, England, GB</t>
-  </si>
-  <si>
     <t>GBP 27010.00 - 27010.00/year</t>
   </si>
   <si>
@@ -1168,6 +2230,120 @@
     <t>https://www.idealist.org/en/nonprofit-job/690ab4f0def040a0958e6ca88b78c7bc-on-purpose-associate-a-leadership-programme-for-social-environmental-impact-on-purpose-london</t>
   </si>
   <si>
+    <t>Operations Specialist</t>
+  </si>
+  <si>
+    <t>EcoLogic Solutions</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/73c07a38e3234463bda2006579049079-operations-specialist-ecologic-solutions-wayne</t>
+  </si>
+  <si>
+    <t>Operations Supervisor</t>
+  </si>
+  <si>
+    <t>CALL Primrose</t>
+  </si>
+  <si>
+    <t>Burlingame, California</t>
+  </si>
+  <si>
+    <t>USD 48.00 - 52.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc01edf470b049cf9b875b7f59046f64-operations-supervisor-call-primrose-burlingame</t>
+  </si>
+  <si>
+    <t>Organizing Director</t>
+  </si>
+  <si>
+    <t>Working Partnerships USA</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7352aff32374727b06d7bb59574d6ee-organizing-director-working-partnerships-usa-san-jose</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>USD 55375.00 - 55375.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/9e5b2200c51043e5b26b9602af3752a3-paralegal-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Part Time Resident Monitor</t>
+  </si>
+  <si>
+    <t>Community Family Life Services</t>
+  </si>
+  <si>
+    <t>USD 18.40 - 18.40/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b6f6ae87ce5497e844a82d8dcca2cb2-part-time-resident-monitor-community-family-life-services-washington</t>
+  </si>
+  <si>
+    <t>Part-Time Development Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Depression and Bipolar Support Alliance</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/280884962bf64fe194c4172629f4d043-part-time-development-operations-coordinator-depression-and-bipolar-support-alliance-chicago</t>
+  </si>
+  <si>
+    <t>Patient Experience &amp; Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Brooklyn Chiropractic Studio PLLC</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/1feb31dd9f3c47eeacea59555da59a6b-patient-experience-operations-coordinator-brooklyn-chiropractic-studio-pllc-kings-county</t>
+  </si>
+  <si>
+    <t>People &amp; Organizational Culture Generalist</t>
+  </si>
+  <si>
+    <t>Portland Japanese Garden</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Environment, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08d3983f0476427386aeecb53f1ebcba-people-organizational-culture-generalist-portland-japanese-garden-portland</t>
+  </si>
+  <si>
     <t>Pessoa Analista de Sensibilização da Sociedade - Nível Pleno - Vaga afirmativa para pessoas negras, indígenas ou PCD</t>
   </si>
   <si>
@@ -1186,6 +2362,117 @@
     <t>https://www.idealist.org/en/nonprofit-job/7d14c7e8b69849d2a88adb4a7fe84706-pessoa-analista-de-sensibilizacao-da-sociedade-nivel-pleno-vaga-afirmativa-para-pessoas-negras-indigenas-ou-pcd-fundacao-maria-cecilia-souto-vidigal-sao-paulo</t>
   </si>
   <si>
+    <t>Planning Fellowship</t>
+  </si>
+  <si>
+    <t>Delaware Valley Regional Planning Commission</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e7488ff7ed248a49a1885fe678a2370-planning-fellowship-delaware-valley-regional-planning-commission-philadelphia</t>
+  </si>
+  <si>
+    <t>Policy Counsel Fellowship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/615a6faab6e84dc79377e53acb092947-policy-counsel-fellowship-citizens-for-responsibility-and-ethics-in-washington-washington</t>
+  </si>
+  <si>
+    <t>Product Manager, Learning Platforms &amp; Impact</t>
+  </si>
+  <si>
+    <t>Generation Citizen</t>
+  </si>
+  <si>
+    <t>USD 66120.00 - 72898.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c94ed64f251b46d99965fec7a731f9a3-product-manager-learning-platforms-impact-generation-citizen-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate, Renewable Energy</t>
+  </si>
+  <si>
+    <t>Great Plains Institute</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b51bc1ab73264706b97d00cb2da2d4c1-program-associate-renewable-energy-great-plains-institute-minneapolis</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/510da5c8e5c74098b2757b212e44423f-program-coordinator-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Biotech CEO Sisterhood</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 65.00/hour</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Job Workplace, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8675c1699ae44a39486fc9fd102cd04-program-director-biotech-ceo-sisterhood-ann-arbor</t>
+  </si>
+  <si>
+    <t>PROGRAM DIRECTOR, NEW ENGLAND</t>
+  </si>
+  <si>
+    <t>USD 91817.00 - 91817.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/263943367c9347c895d107e22da49347-program-director-new-england-generation-citizen-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebce1fa96ceb4b259bd2e9c639e47788-program-manager-meet-the-moment-nh-manchester</t>
+  </si>
+  <si>
+    <t>QUALITY AND OPERATIONS PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Association for Community Affiliated Plans</t>
+  </si>
+  <si>
+    <t>Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7959d5c51a8f493a823b82df49ef6d30-quality-and-operations-program-associate-association-for-community-affiliated-plans-washington</t>
+  </si>
+  <si>
     <t>Research Scientist I (Clinical Development Department) [Based in Kigali]</t>
   </si>
   <si>
@@ -1195,12 +2482,102 @@
     <t>Kigali, Kigali City, RW</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d6a0975ae4094fc299b6d9086bc9e229-research-scientist-i-clinical-development-department-based-in-kigali-international-vaccine-institute-kigali</t>
   </si>
   <si>
+    <t>Sales Associate - Outbound Calling</t>
+  </si>
+  <si>
+    <t>Better Business Bureau of Long Island</t>
+  </si>
+  <si>
+    <t>Farmingdale, New York</t>
+  </si>
+  <si>
+    <t>USD 17.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6bd26d76725a44ba9b79cd48d833b8fe-sales-associate-outbound-calling-better-business-bureau-of-long-island-farmingdale</t>
+  </si>
+  <si>
+    <t>Senior Data Analyst (5469C), California Policy Lab #88224</t>
+  </si>
+  <si>
+    <t>University of California, Berkeley</t>
+  </si>
+  <si>
+    <t>Berkeley, CA</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c63ed9e1ce564cb88afeedf0685d5cda-senior-data-analyst-5469c-california-policy-lab-88224-university-of-california-berkeley-berkeley</t>
+  </si>
+  <si>
+    <t>Senior Development Manager, Carolinas Chapter</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd7190bf0f6646e0897720bacb824343-senior-development-manager-carolinas-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Senior Director, Data Operations</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7532de7fb8147808e921d8b286e9e26-senior-director-data-operations-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Senior Manager, Clinical Services</t>
+  </si>
+  <si>
+    <t>Friends of Ruby</t>
+  </si>
+  <si>
+    <t>Toronto, Ontario, CA</t>
+  </si>
+  <si>
+    <t>CAD 101911.00 - 106028.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5dbbbdb287f24e7fa18d9635f85cb147-senior-manager-clinical-services-friends-of-ruby-toronto</t>
+  </si>
+  <si>
+    <t>Senior Program Officer</t>
+  </si>
+  <si>
+    <t>Pride Foundation</t>
+  </si>
+  <si>
+    <t>USD 89000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60086526a6be46c98cfd43258d70e5ca-senior-program-officer-pride-foundation-seattle</t>
+  </si>
+  <si>
+    <t>Senior Technical Editor</t>
+  </si>
+  <si>
+    <t>American Association of State Highway &amp; Transportation Officials</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42189f182e8c48c38da44a04c245035e-senior-technical-editor-american-association-of-state-highway-transportation-officials-washington</t>
+  </si>
+  <si>
     <t>Site Manager</t>
   </si>
   <si>
@@ -1210,15 +2587,39 @@
     <t>Takoma Park, MD</t>
   </si>
   <si>
-    <t>USD 50000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>Disability, Health Medicine, Hunger Food Security</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/72107cffb84a442890abea0bc0392ef6-site-manager-meals-on-wheels-of-takoma-parksilver-spring-takoma-park</t>
   </si>
   <si>
+    <t>SNACC Afterschool Chef and Food Educator</t>
+  </si>
+  <si>
+    <t>SNACC Inc.</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52f57ebe2a3e4578be5c0afd70c0bfc8-snacc-afterschool-chef-and-food-educator-snacc-inc-new-york</t>
+  </si>
+  <si>
+    <t>Social Enterprise Manager - Catering &amp; Contract Meal Program</t>
+  </si>
+  <si>
+    <t>Trenton Area Soup Kitchen</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94c494fc788e4f45ab32f2bd0a8cdd94-social-enterprise-manager-catering-contract-meal-program-trenton-area-soup-kitchen-trenton</t>
+  </si>
+  <si>
     <t>Southern Maine Community Outreach Manager</t>
   </si>
   <si>
@@ -1231,10 +2632,748 @@
     <t>USD 53000.00 - 63000.00/year</t>
   </si>
   <si>
-    <t>Climate Change, Environment, Civic Engagement</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/a3fc900e616d482a8bc656f0b62fe740-southern-maine-community-outreach-manager-maine-coast-heritage-trust-topsham</t>
+  </si>
+  <si>
+    <t>Special Assistant to the President &amp; CEO (Association Office)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee8b88c84b5846a2bf09d032a34108aa-special-assistant-to-the-president-ceo-association-office-ymca-of-greater-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Special Education Coordinator</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6bacba17e1d4c0e8b2dc4e8bc4b37c7-special-education-coordinator-uncommon-schools-new-york</t>
+  </si>
+  <si>
+    <t>Sr. Social Worker</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16f18aa44c904430976e9fbed69fe00c-sr-social-worker-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Santa Clara Valley Open Space Authority</t>
+  </si>
+  <si>
+    <t>USD 48.09 - 58.45/hour</t>
+  </si>
+  <si>
+    <t>Environment, Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/05fc211281cf47b480e9953af55de738-staff-accountant-santa-clara-valley-open-space-authority-san-jose</t>
+  </si>
+  <si>
+    <t>MCE Social Capital</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Philanthropy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1b2e846f98a4fdba60de17a34816fad-staff-accountant-mce-social-capital-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Immigration Law</t>
+  </si>
+  <si>
+    <t>Greater Boston Legal Services</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 82500.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02e4d20d620c4025b61a8f7a605df084-staff-attorney-immigration-law-greater-boston-legal-services-boston</t>
+  </si>
+  <si>
+    <t>Staff Attorney (Maryland)</t>
+  </si>
+  <si>
+    <t>Council on American-Islamic Relations - National Headquarters</t>
+  </si>
+  <si>
+    <t>Remote (Maryland)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 83100.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a569af37b3064633a40e31c72573f69d-staff-attorney-maryland-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney II-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21a704212ddc4017bccfe7e8abdd708d-staff-attorney-ii-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Supervising Staff Attorney, Immigration</t>
+  </si>
+  <si>
+    <t>U.S. Court of Appeals, Ninth Circuit</t>
+  </si>
+  <si>
+    <t>USD 184950.00 - 184950.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/97919a0ce9354245a71cb5abdf530dd2-supervising-staff-attorney-immigration-us-court-of-appeals-ninth-circuit-san-francisco</t>
+  </si>
+  <si>
+    <t>Tracker/Field Researcher (GA)</t>
+  </si>
+  <si>
+    <t>American Bridge 21st Century</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9d2c0cf94e04e4daae12a2d095169d8-trackerfield-researcher-ga-american-bridge-21st-century-atlanta</t>
+  </si>
+  <si>
+    <t>Web Content Coordinator</t>
+  </si>
+  <si>
+    <t>American Society of Clinical Oncology</t>
+  </si>
+  <si>
+    <t>USD 29.79 - 39.18/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7f0d20d365a41c0b2f9929732588220-web-content-coordinator-american-society-of-clinical-oncology-alexandria</t>
+  </si>
+  <si>
+    <t>AGRICULTURAL PRODUCTION COORDINATOR</t>
+  </si>
+  <si>
+    <t>San Antonio Food Bank</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72371407</t>
+  </si>
+  <si>
+    <t>ASSISTANT COORDINATOR</t>
+  </si>
+  <si>
+    <t>CHEESE INDUSTRY AND APPLICATIONS - Center for Dairy Research</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72366519</t>
+  </si>
+  <si>
+    <t>ASSISTANT ENGAGEMENT PRODUCER</t>
+  </si>
+  <si>
+    <t>The Food and Environment Reporting Network</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72403179</t>
+  </si>
+  <si>
+    <t>ASSISTANT OPERATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>Spruce Head Fishermens Cooperative</t>
+  </si>
+  <si>
+    <t>South Thomaston, Maine</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72367741</t>
+  </si>
+  <si>
+    <t>BRAIDING SEEDS FELLOWSHIP</t>
+  </si>
+  <si>
+    <t>Soul Fire Farm</t>
+  </si>
+  <si>
+    <t>Varied, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72400735</t>
+  </si>
+  <si>
+    <t>BUSINESS DEVELOPMENT MANAGER</t>
+  </si>
+  <si>
+    <t>NORTH AMERICA - GREENHOUSE AND HORTICULTURE - Cravo Equipment</t>
+  </si>
+  <si>
+    <t>Brantford, Ontario</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72409289</t>
+  </si>
+  <si>
+    <t>CHIEF FINANCIAL OFFICER</t>
+  </si>
+  <si>
+    <t>Rodale Institute</t>
+  </si>
+  <si>
+    <t>Kutztown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72404401</t>
+  </si>
+  <si>
+    <t>CHIEF OF STAFF</t>
+  </si>
+  <si>
+    <t>Community FoodBank of New Jersey</t>
+  </si>
+  <si>
+    <t>Hillside, New Jersey</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72387293</t>
+  </si>
+  <si>
+    <t>COMMUNICATIONS DIRECTOR</t>
+  </si>
+  <si>
+    <t>Friends of Family Farmers</t>
+  </si>
+  <si>
+    <t>Junction City, Oregon</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72417843</t>
+  </si>
+  <si>
+    <t>COMMUNITY FOOD SYSTEMS PLANNER</t>
+  </si>
+  <si>
+    <t>Kokua Kalihi Valley Comprehensive Family Services</t>
+  </si>
+  <si>
+    <t>Kalihi Valley, Oahu, Hawaii</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72373851</t>
+  </si>
+  <si>
+    <t>DATA ANALYST</t>
+  </si>
+  <si>
+    <t>Building Impact Through Eaters</t>
+  </si>
+  <si>
+    <t>Hybrid in Anaheim, CA, California</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72375073</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>The Farmlink Project</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72401957</t>
+  </si>
+  <si>
+    <t>DIGITAL ENGAGEMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>Canadian Centre for Food and Ecology</t>
+  </si>
+  <si>
+    <t>Hybrid in Toronto, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72415399</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF JEFFERSON FARM AND GARDENS EXTENSION AND EDUCATION CENTER AND FIELD SPECIALIST IN AGRICULTURAL BUSINESS</t>
+  </si>
+  <si>
+    <t>University of Missouri</t>
+  </si>
+  <si>
+    <t>Columbia, Missouri</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72365297</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF OPERATIONS</t>
+  </si>
+  <si>
+    <t>Carbon Yield</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72397069</t>
+  </si>
+  <si>
+    <t>The New Farm Centre</t>
+  </si>
+  <si>
+    <t>Creemore, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72414177</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF PROGRAMS</t>
+  </si>
+  <si>
+    <t>Food System Six</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72406845</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF RESEARCH</t>
+  </si>
+  <si>
+    <t>Central Texas Food Bank</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72386071</t>
+  </si>
+  <si>
+    <t>DISTRIBUTION MANAGER</t>
+  </si>
+  <si>
+    <t>Newton Food Pantry</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72411733</t>
+  </si>
+  <si>
+    <t>ENTERPRISE BUSINESS TECHNOLOGY DIRECTOR</t>
+  </si>
+  <si>
+    <t>National Coop Grocers</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72388515</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Monadnock Grown Coalition</t>
+  </si>
+  <si>
+    <t>Remote Position with Regular In-Person Engagement</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72357965</t>
+  </si>
+  <si>
+    <t>EXTENSION EDUCATOR</t>
+  </si>
+  <si>
+    <t>FIELD AND FORAGE CROPS - Penn State</t>
+  </si>
+  <si>
+    <t>Blair County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72360409</t>
+  </si>
+  <si>
+    <t>FARM MANAGEMENT OUTREACH SPECIALIST</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72361631</t>
+  </si>
+  <si>
+    <t>FIELD CREW</t>
+  </si>
+  <si>
+    <t>Land Sakes Farm</t>
+  </si>
+  <si>
+    <t>Weston, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72354299</t>
+  </si>
+  <si>
+    <t>GENERAL MANAGER</t>
+  </si>
+  <si>
+    <t>The Common Market</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72383627</t>
+  </si>
+  <si>
+    <t>KLINGBEIL ENDOWED DEPARTMENT HEAD AND PROFESSOR</t>
+  </si>
+  <si>
+    <t>DEPARTMENT OF AGRICULTURAL AND BIOSYSTEMS ENGINEERING - South Dakota State University</t>
+  </si>
+  <si>
+    <t>Brookings, South Dakota</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72359187</t>
+  </si>
+  <si>
+    <t>LAND AND WATER PROGRAM DIRECTOR</t>
+  </si>
+  <si>
+    <t>Western Landowners Alliance</t>
+  </si>
+  <si>
+    <t>Remote with required residency in the American Wes</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72389737</t>
+  </si>
+  <si>
+    <t>LOCAL FOOD SALES TERRITORY MANAGER</t>
+  </si>
+  <si>
+    <t>Hybrid in Houston, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72382405</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>NEIGHBORS ADVOCACY - Feeding America</t>
+  </si>
+  <si>
+    <t>Hybrid in Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72350633</t>
+  </si>
+  <si>
+    <t>MARKET GARDEN MANAGER</t>
+  </si>
+  <si>
+    <t>Gorman Heritage Farm</t>
+  </si>
+  <si>
+    <t>Cincinnati, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72392181</t>
+  </si>
+  <si>
+    <t>MARKETING AND COMMUNICATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Ontario Soil Network</t>
+  </si>
+  <si>
+    <t>Remote, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72405623</t>
+  </si>
+  <si>
+    <t>MOBILE AND FARM MARKET ASSISTANT COORDINATOR</t>
+  </si>
+  <si>
+    <t>Buffalo Go Green</t>
+  </si>
+  <si>
+    <t>Buffalo, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72399513</t>
+  </si>
+  <si>
+    <t>NEW ROOTS FARM COORDINATOR</t>
+  </si>
+  <si>
+    <t>International Rescue Committee</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72408067</t>
+  </si>
+  <si>
+    <t>NORTH AMERICAN AG PORTFOLIO AND LEARNING MANAGER</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72377517</t>
+  </si>
+  <si>
+    <t>PART TIME CLASSROOM EDUCATOR</t>
+  </si>
+  <si>
+    <t>Green Beetz</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72362853</t>
+  </si>
+  <si>
+    <t>PART TIME NUTRITION INTEGRATION SPECIALIST</t>
+  </si>
+  <si>
+    <t>Michigan Primary Care Association</t>
+  </si>
+  <si>
+    <t>Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72364075</t>
+  </si>
+  <si>
+    <t>PLANT SCIENCE EDUCATOR</t>
+  </si>
+  <si>
+    <t>Donald Danforth Plant Science Center</t>
+  </si>
+  <si>
+    <t>St Louis, Missouri</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72356743</t>
+  </si>
+  <si>
+    <t>POLICY MANAGER</t>
+  </si>
+  <si>
+    <t>Torrey Advisory Group</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72419065</t>
+  </si>
+  <si>
+    <t>PRODUCTION AND DELIVERY SENIOR ASSISTANT</t>
+  </si>
+  <si>
+    <t>Victoria Community Food Hub Society</t>
+  </si>
+  <si>
+    <t>Esquimalt, British Columbia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72416621</t>
+  </si>
+  <si>
+    <t>PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Kids in Nutrition</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72395847</t>
+  </si>
+  <si>
+    <t>PROJECT ASSISTANT</t>
+  </si>
+  <si>
+    <t>REGIONAL SUSTAINABLE DEVELOPMENT PARTNERSHIPS - University of Minnesota</t>
+  </si>
+  <si>
+    <t>Twin Cities, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72398291</t>
+  </si>
+  <si>
+    <t>RESEARCH SUPPORT SPECIALIST</t>
+  </si>
+  <si>
+    <t>University of Buffalo</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72410511</t>
+  </si>
+  <si>
+    <t>SENIOR DIRECTOR</t>
+  </si>
+  <si>
+    <t>FOOD IS MEDICINE - Federation of Virginia Food Banks</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72412955</t>
+  </si>
+  <si>
+    <t>SENIOR FARM MANAGER</t>
+  </si>
+  <si>
+    <t>Agmenity</t>
+  </si>
+  <si>
+    <t>Martin County, Florida</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72376295</t>
+  </si>
+  <si>
+    <t>SENIOR MANAGER OF AGRICULTURAL RELATIONS</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72381183</t>
+  </si>
+  <si>
+    <t>SPECIAL ASSISTANT TO THE PRESIDENT AND CEO</t>
+  </si>
+  <si>
+    <t>Capital Area Food Bank</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72355521</t>
+  </si>
+  <si>
+    <t>SPECIALIST</t>
+  </si>
+  <si>
+    <t>GOVERNMENT AFFAIRS - Feeding America</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72378739</t>
+  </si>
+  <si>
+    <t>STRATEGIC INITIATIVES DIRECTOR</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72390959</t>
+  </si>
+  <si>
+    <t>TEXAS AGRICULTURE SPECIALIST</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Remote, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72379961</t>
+  </si>
+  <si>
+    <t>WAREHOUSE ASSOCIATION</t>
+  </si>
+  <si>
+    <t>SEASONAL - The Common Market</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72384849</t>
+  </si>
+  <si>
+    <t>WRITER COMMUNICATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>Food Allergy Research and Education</t>
+  </si>
+  <si>
+    <t>McLean, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72370185</t>
+  </si>
+  <si>
+    <t>WRP WAREHOUSE MANAGER</t>
+  </si>
+  <si>
+    <t>Food Forward</t>
+  </si>
+  <si>
+    <t>Bell, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72368963</t>
   </si>
 </sst>
 </file>
@@ -2558,7 +4697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2597,8 +4736,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2606,7 +4795,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2647,413 +4836,413 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
         <v>210</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D3" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F7" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D8" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F8" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>246</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B10" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F10" t="s">
-        <v>252</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B11" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E11" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F11" t="s">
-        <v>258</v>
+        <v>43</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B12" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C12" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="D12" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F12" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E13" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>278</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="C15" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E15" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="F15" t="s">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C16" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="D17" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="E17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D18" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F19" t="s">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>304</v>
@@ -3067,433 +5256,3032 @@
         <v>306</v>
       </c>
       <c r="C20" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="D20" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B21" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D21" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D22" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>320</v>
       </c>
       <c r="F22" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B23" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C23" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D23" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F23" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B24" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C24" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D24" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F24" t="s">
-        <v>330</v>
+        <v>43</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C25" t="s">
-        <v>334</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="E25" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B26" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s">
-        <v>340</v>
+        <v>223</v>
       </c>
       <c r="E26" t="s">
+        <v>284</v>
+      </c>
+      <c r="F26" t="s">
         <v>341</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>343</v>
+      </c>
+      <c r="B27" t="s">
         <v>344</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>345</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>223</v>
+      </c>
+      <c r="E27" t="s">
         <v>346</v>
       </c>
-      <c r="D27" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>347</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>349</v>
+      </c>
+      <c r="B28" t="s">
+        <v>344</v>
+      </c>
+      <c r="C28" t="s">
+        <v>345</v>
+      </c>
+      <c r="D28" t="s">
+        <v>223</v>
+      </c>
+      <c r="E28" t="s">
+        <v>346</v>
+      </c>
+      <c r="F28" t="s">
+        <v>347</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="B28" t="s">
-        <v>351</v>
-      </c>
-      <c r="C28" t="s">
-        <v>229</v>
-      </c>
-      <c r="D28" t="s">
-        <v>211</v>
-      </c>
-      <c r="E28" t="s">
-        <v>352</v>
-      </c>
-      <c r="F28" t="s">
-        <v>353</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B29" t="s">
+        <v>352</v>
+      </c>
+      <c r="C29" t="s">
+        <v>353</v>
+      </c>
+      <c r="D29" t="s">
+        <v>223</v>
+      </c>
+      <c r="E29" t="s">
+        <v>354</v>
+      </c>
+      <c r="F29" t="s">
         <v>355</v>
       </c>
-      <c r="B29" t="s">
+      <c r="H29" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="C29" t="s">
-        <v>210</v>
-      </c>
-      <c r="D29" t="s">
-        <v>211</v>
-      </c>
-      <c r="E29" t="s">
-        <v>357</v>
-      </c>
-      <c r="F29" t="s">
-        <v>358</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>357</v>
+      </c>
+      <c r="B30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" t="s">
+        <v>223</v>
+      </c>
+      <c r="E30" t="s">
+        <v>284</v>
+      </c>
+      <c r="F30" t="s">
+        <v>359</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B30" t="s">
-        <v>261</v>
-      </c>
-      <c r="C30" t="s">
-        <v>229</v>
-      </c>
-      <c r="D30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" t="s">
-        <v>361</v>
-      </c>
-      <c r="F30" t="s">
-        <v>362</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" t="s">
+        <v>264</v>
+      </c>
+      <c r="D31" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" t="s">
+        <v>363</v>
+      </c>
+      <c r="F31" t="s">
         <v>364</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H31" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C31" t="s">
-        <v>346</v>
-      </c>
-      <c r="D31" t="s">
-        <v>211</v>
-      </c>
-      <c r="E31" t="s">
-        <v>366</v>
-      </c>
-      <c r="F31" t="s">
-        <v>367</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>366</v>
+      </c>
+      <c r="B32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C32" t="s">
+        <v>368</v>
+      </c>
+      <c r="D32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E32" t="s">
         <v>369</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F32" t="s">
         <v>370</v>
       </c>
-      <c r="C32" t="s">
-        <v>229</v>
-      </c>
-      <c r="D32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="H32" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="F32" t="s">
-        <v>372</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>372</v>
+      </c>
+      <c r="B33" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" t="s">
+        <v>264</v>
+      </c>
+      <c r="D33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E33" t="s">
+        <v>373</v>
+      </c>
+      <c r="F33" t="s">
+        <v>255</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="B33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C33" t="s">
-        <v>375</v>
-      </c>
-      <c r="D33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E33" t="s">
-        <v>376</v>
-      </c>
-      <c r="F33" t="s">
-        <v>43</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>375</v>
+      </c>
+      <c r="B34" t="s">
+        <v>376</v>
+      </c>
+      <c r="C34" t="s">
+        <v>377</v>
+      </c>
+      <c r="D34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" t="s">
         <v>378</v>
       </c>
-      <c r="B34" t="s">
+      <c r="F34" t="s">
         <v>379</v>
       </c>
-      <c r="C34" t="s">
+      <c r="H34" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="D34" t="s">
-        <v>340</v>
-      </c>
-      <c r="E34" t="s">
-        <v>381</v>
-      </c>
-      <c r="F34" t="s">
-        <v>382</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>381</v>
+      </c>
+      <c r="B35" t="s">
+        <v>382</v>
+      </c>
+      <c r="C35" t="s">
+        <v>264</v>
+      </c>
+      <c r="D35" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" t="s">
+        <v>383</v>
+      </c>
+      <c r="F35" t="s">
         <v>384</v>
       </c>
-      <c r="B35" t="s">
+      <c r="H35" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C35" t="s">
-        <v>386</v>
-      </c>
-      <c r="D35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E35" t="s">
-        <v>387</v>
-      </c>
-      <c r="F35" t="s">
-        <v>388</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>386</v>
+      </c>
+      <c r="B36" t="s">
+        <v>387</v>
+      </c>
+      <c r="C36" t="s">
+        <v>388</v>
+      </c>
+      <c r="D36" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36" t="s">
+        <v>389</v>
+      </c>
+      <c r="F36" t="s">
+        <v>43</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="B36" t="s">
-        <v>391</v>
-      </c>
-      <c r="C36" t="s">
-        <v>392</v>
-      </c>
-      <c r="D36" t="s">
-        <v>211</v>
-      </c>
-      <c r="E36" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" t="s">
-        <v>393</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>391</v>
+      </c>
+      <c r="B37" t="s">
+        <v>392</v>
+      </c>
+      <c r="C37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" t="s">
+        <v>393</v>
+      </c>
+      <c r="F37" t="s">
+        <v>394</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B37" t="s">
-        <v>396</v>
-      </c>
-      <c r="C37" t="s">
-        <v>397</v>
-      </c>
-      <c r="D37" t="s">
-        <v>211</v>
-      </c>
-      <c r="E37" t="s">
-        <v>398</v>
-      </c>
-      <c r="F37" t="s">
-        <v>399</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>396</v>
+      </c>
+      <c r="B38" t="s">
+        <v>397</v>
+      </c>
+      <c r="C38" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E38" t="s">
+        <v>398</v>
+      </c>
+      <c r="F38" t="s">
+        <v>399</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>401</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>402</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>403</v>
       </c>
-      <c r="D38" t="s">
-        <v>211</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="D39" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" t="s">
         <v>404</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>405</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H39" s="2" t="s">
         <v>406</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>407</v>
+      </c>
+      <c r="B40" t="s">
+        <v>408</v>
+      </c>
+      <c r="C40" t="s">
+        <v>264</v>
+      </c>
+      <c r="D40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E40" t="s">
+        <v>409</v>
+      </c>
+      <c r="F40" t="s">
+        <v>410</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>412</v>
+      </c>
+      <c r="B41" t="s">
+        <v>413</v>
+      </c>
+      <c r="C41" t="s">
+        <v>414</v>
+      </c>
+      <c r="D41" t="s">
+        <v>289</v>
+      </c>
+      <c r="E41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" t="s">
+        <v>415</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>417</v>
+      </c>
+      <c r="B42" t="s">
+        <v>418</v>
+      </c>
+      <c r="C42" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" t="s">
+        <v>419</v>
+      </c>
+      <c r="F42" t="s">
+        <v>420</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>422</v>
+      </c>
+      <c r="B43" t="s">
+        <v>387</v>
+      </c>
+      <c r="C43" t="s">
+        <v>388</v>
+      </c>
+      <c r="D43" t="s">
+        <v>223</v>
+      </c>
+      <c r="E43" t="s">
+        <v>423</v>
+      </c>
+      <c r="F43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>425</v>
+      </c>
+      <c r="B44" t="s">
+        <v>426</v>
+      </c>
+      <c r="C44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
+        <v>302</v>
+      </c>
+      <c r="E44" t="s">
+        <v>427</v>
+      </c>
+      <c r="F44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>429</v>
+      </c>
+      <c r="B45" t="s">
+        <v>430</v>
+      </c>
+      <c r="C45" t="s">
+        <v>431</v>
+      </c>
+      <c r="D45" t="s">
+        <v>223</v>
+      </c>
+      <c r="E45" t="s">
+        <v>398</v>
+      </c>
+      <c r="F45" t="s">
+        <v>432</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>434</v>
+      </c>
+      <c r="B46" t="s">
+        <v>435</v>
+      </c>
+      <c r="C46" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" t="s">
+        <v>289</v>
+      </c>
+      <c r="E46" t="s">
+        <v>436</v>
+      </c>
+      <c r="F46" t="s">
+        <v>437</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>439</v>
+      </c>
+      <c r="B47" t="s">
+        <v>440</v>
+      </c>
+      <c r="C47" t="s">
+        <v>441</v>
+      </c>
+      <c r="D47" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" t="s">
+        <v>442</v>
+      </c>
+      <c r="F47" t="s">
+        <v>443</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>445</v>
+      </c>
+      <c r="B48" t="s">
+        <v>446</v>
+      </c>
+      <c r="C48" t="s">
+        <v>447</v>
+      </c>
+      <c r="D48" t="s">
+        <v>223</v>
+      </c>
+      <c r="E48" t="s">
+        <v>448</v>
+      </c>
+      <c r="F48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>450</v>
+      </c>
+      <c r="B49" t="s">
+        <v>451</v>
+      </c>
+      <c r="C49" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" t="s">
+        <v>452</v>
+      </c>
+      <c r="E49" t="s">
+        <v>453</v>
+      </c>
+      <c r="F49" t="s">
+        <v>454</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>456</v>
+      </c>
+      <c r="B50" t="s">
+        <v>457</v>
+      </c>
+      <c r="C50" t="s">
+        <v>458</v>
+      </c>
+      <c r="D50" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" t="s">
+        <v>459</v>
+      </c>
+      <c r="F50" t="s">
+        <v>43</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>461</v>
+      </c>
+      <c r="B51" t="s">
+        <v>462</v>
+      </c>
+      <c r="C51" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" t="s">
+        <v>463</v>
+      </c>
+      <c r="F51" t="s">
+        <v>464</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>466</v>
+      </c>
+      <c r="B52" t="s">
+        <v>467</v>
+      </c>
+      <c r="C52" t="s">
+        <v>468</v>
+      </c>
+      <c r="D52" t="s">
+        <v>223</v>
+      </c>
+      <c r="E52" t="s">
+        <v>469</v>
+      </c>
+      <c r="F52" t="s">
+        <v>470</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>472</v>
+      </c>
+      <c r="B53" t="s">
+        <v>473</v>
+      </c>
+      <c r="C53" t="s">
+        <v>474</v>
+      </c>
+      <c r="D53" t="s">
+        <v>223</v>
+      </c>
+      <c r="E53" t="s">
+        <v>398</v>
+      </c>
+      <c r="F53" t="s">
+        <v>475</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>477</v>
+      </c>
+      <c r="B54" t="s">
+        <v>478</v>
+      </c>
+      <c r="C54" t="s">
+        <v>269</v>
+      </c>
+      <c r="D54" t="s">
+        <v>223</v>
+      </c>
+      <c r="E54" t="s">
+        <v>479</v>
+      </c>
+      <c r="F54" t="s">
+        <v>480</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>482</v>
+      </c>
+      <c r="B55" t="s">
+        <v>483</v>
+      </c>
+      <c r="C55" t="s">
+        <v>259</v>
+      </c>
+      <c r="D55" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" t="s">
+        <v>484</v>
+      </c>
+      <c r="F55" t="s">
+        <v>485</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>487</v>
+      </c>
+      <c r="B56" t="s">
+        <v>488</v>
+      </c>
+      <c r="C56" t="s">
+        <v>489</v>
+      </c>
+      <c r="D56" t="s">
+        <v>289</v>
+      </c>
+      <c r="E56" t="s">
+        <v>490</v>
+      </c>
+      <c r="F56" t="s">
+        <v>491</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>493</v>
+      </c>
+      <c r="B57" t="s">
+        <v>494</v>
+      </c>
+      <c r="C57" t="s">
+        <v>259</v>
+      </c>
+      <c r="D57" t="s">
+        <v>223</v>
+      </c>
+      <c r="E57" t="s">
+        <v>495</v>
+      </c>
+      <c r="F57" t="s">
+        <v>496</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>493</v>
+      </c>
+      <c r="B58" t="s">
+        <v>498</v>
+      </c>
+      <c r="C58" t="s">
+        <v>499</v>
+      </c>
+      <c r="D58" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" t="s">
+        <v>500</v>
+      </c>
+      <c r="F58" t="s">
+        <v>501</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>503</v>
+      </c>
+      <c r="B59" t="s">
+        <v>504</v>
+      </c>
+      <c r="C59" t="s">
+        <v>259</v>
+      </c>
+      <c r="D59" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" t="s">
+        <v>505</v>
+      </c>
+      <c r="F59" t="s">
+        <v>506</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>503</v>
+      </c>
+      <c r="B60" t="s">
+        <v>504</v>
+      </c>
+      <c r="C60" t="s">
+        <v>431</v>
+      </c>
+      <c r="D60" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" t="s">
+        <v>505</v>
+      </c>
+      <c r="F60" t="s">
+        <v>506</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>509</v>
+      </c>
+      <c r="B61" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" t="s">
+        <v>510</v>
+      </c>
+      <c r="D61" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" t="s">
+        <v>511</v>
+      </c>
+      <c r="F61" t="s">
+        <v>236</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>513</v>
+      </c>
+      <c r="B62" t="s">
+        <v>514</v>
+      </c>
+      <c r="C62" t="s">
+        <v>259</v>
+      </c>
+      <c r="D62" t="s">
+        <v>223</v>
+      </c>
+      <c r="E62" t="s">
+        <v>515</v>
+      </c>
+      <c r="F62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>517</v>
+      </c>
+      <c r="B63" t="s">
+        <v>518</v>
+      </c>
+      <c r="C63" t="s">
+        <v>325</v>
+      </c>
+      <c r="D63" t="s">
+        <v>223</v>
+      </c>
+      <c r="E63" t="s">
+        <v>519</v>
+      </c>
+      <c r="F63" t="s">
+        <v>520</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>517</v>
+      </c>
+      <c r="B64" t="s">
+        <v>522</v>
+      </c>
+      <c r="C64" t="s">
+        <v>523</v>
+      </c>
+      <c r="D64" t="s">
+        <v>223</v>
+      </c>
+      <c r="E64" t="s">
+        <v>524</v>
+      </c>
+      <c r="F64" t="s">
+        <v>525</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>527</v>
+      </c>
+      <c r="B65" t="s">
+        <v>528</v>
+      </c>
+      <c r="C65" t="s">
+        <v>529</v>
+      </c>
+      <c r="D65" t="s">
+        <v>223</v>
+      </c>
+      <c r="E65" t="s">
+        <v>530</v>
+      </c>
+      <c r="F65" t="s">
+        <v>531</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>533</v>
+      </c>
+      <c r="B66" t="s">
+        <v>534</v>
+      </c>
+      <c r="C66" t="s">
+        <v>535</v>
+      </c>
+      <c r="D66" t="s">
+        <v>289</v>
+      </c>
+      <c r="E66" t="s">
+        <v>536</v>
+      </c>
+      <c r="F66" t="s">
+        <v>537</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>539</v>
+      </c>
+      <c r="B67" t="s">
+        <v>540</v>
+      </c>
+      <c r="C67" t="s">
+        <v>353</v>
+      </c>
+      <c r="D67" t="s">
+        <v>223</v>
+      </c>
+      <c r="E67" t="s">
+        <v>541</v>
+      </c>
+      <c r="F67" t="s">
+        <v>542</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>544</v>
+      </c>
+      <c r="B68" t="s">
+        <v>545</v>
+      </c>
+      <c r="C68" t="s">
+        <v>264</v>
+      </c>
+      <c r="D68" t="s">
+        <v>223</v>
+      </c>
+      <c r="E68" t="s">
+        <v>546</v>
+      </c>
+      <c r="F68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>549</v>
+      </c>
+      <c r="B69" t="s">
+        <v>550</v>
+      </c>
+      <c r="C69" t="s">
+        <v>551</v>
+      </c>
+      <c r="D69" t="s">
+        <v>223</v>
+      </c>
+      <c r="E69" t="s">
+        <v>524</v>
+      </c>
+      <c r="F69" t="s">
+        <v>552</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>554</v>
+      </c>
+      <c r="B70" t="s">
+        <v>555</v>
+      </c>
+      <c r="C70" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" t="s">
+        <v>223</v>
+      </c>
+      <c r="E70" t="s">
+        <v>556</v>
+      </c>
+      <c r="F70" t="s">
+        <v>557</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>559</v>
+      </c>
+      <c r="B71" t="s">
+        <v>560</v>
+      </c>
+      <c r="C71" t="s">
+        <v>264</v>
+      </c>
+      <c r="D71" t="s">
+        <v>223</v>
+      </c>
+      <c r="E71" t="s">
+        <v>561</v>
+      </c>
+      <c r="F71" t="s">
+        <v>562</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>564</v>
+      </c>
+      <c r="B72" t="s">
+        <v>565</v>
+      </c>
+      <c r="C72" t="s">
+        <v>259</v>
+      </c>
+      <c r="D72" t="s">
+        <v>223</v>
+      </c>
+      <c r="E72" t="s">
+        <v>566</v>
+      </c>
+      <c r="F72" t="s">
+        <v>567</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>569</v>
+      </c>
+      <c r="B73" t="s">
+        <v>570</v>
+      </c>
+      <c r="C73" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73" t="s">
+        <v>223</v>
+      </c>
+      <c r="E73" t="s">
+        <v>571</v>
+      </c>
+      <c r="F73" t="s">
+        <v>43</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>573</v>
+      </c>
+      <c r="B74" t="s">
+        <v>574</v>
+      </c>
+      <c r="C74" t="s">
+        <v>575</v>
+      </c>
+      <c r="D74" t="s">
+        <v>223</v>
+      </c>
+      <c r="E74" t="s">
+        <v>576</v>
+      </c>
+      <c r="F74" t="s">
+        <v>577</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>579</v>
+      </c>
+      <c r="B75" t="s">
+        <v>580</v>
+      </c>
+      <c r="C75" t="s">
+        <v>581</v>
+      </c>
+      <c r="D75" t="s">
+        <v>223</v>
+      </c>
+      <c r="E75" t="s">
+        <v>43</v>
+      </c>
+      <c r="F75" t="s">
+        <v>582</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>579</v>
+      </c>
+      <c r="B76" t="s">
+        <v>584</v>
+      </c>
+      <c r="C76" t="s">
+        <v>585</v>
+      </c>
+      <c r="D76" t="s">
+        <v>223</v>
+      </c>
+      <c r="E76" t="s">
+        <v>586</v>
+      </c>
+      <c r="F76" t="s">
+        <v>587</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>589</v>
+      </c>
+      <c r="B77" t="s">
+        <v>590</v>
+      </c>
+      <c r="C77" t="s">
+        <v>591</v>
+      </c>
+      <c r="D77" t="s">
+        <v>223</v>
+      </c>
+      <c r="E77" t="s">
+        <v>592</v>
+      </c>
+      <c r="F77" t="s">
+        <v>593</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>595</v>
+      </c>
+      <c r="B78" t="s">
+        <v>596</v>
+      </c>
+      <c r="C78" t="s">
+        <v>597</v>
+      </c>
+      <c r="D78" t="s">
+        <v>223</v>
+      </c>
+      <c r="E78" t="s">
+        <v>524</v>
+      </c>
+      <c r="F78" t="s">
+        <v>598</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>600</v>
+      </c>
+      <c r="B79" t="s">
+        <v>601</v>
+      </c>
+      <c r="C79" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" t="s">
+        <v>223</v>
+      </c>
+      <c r="E79" t="s">
+        <v>602</v>
+      </c>
+      <c r="F79" t="s">
+        <v>285</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>604</v>
+      </c>
+      <c r="B80" t="s">
+        <v>601</v>
+      </c>
+      <c r="C80" t="s">
+        <v>269</v>
+      </c>
+      <c r="D80" t="s">
+        <v>223</v>
+      </c>
+      <c r="E80" t="s">
+        <v>605</v>
+      </c>
+      <c r="F80" t="s">
+        <v>606</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>608</v>
+      </c>
+      <c r="B81" t="s">
+        <v>609</v>
+      </c>
+      <c r="C81" t="s">
+        <v>610</v>
+      </c>
+      <c r="D81" t="s">
+        <v>611</v>
+      </c>
+      <c r="E81" t="s">
+        <v>612</v>
+      </c>
+      <c r="F81" t="s">
+        <v>613</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>615</v>
+      </c>
+      <c r="B82" t="s">
+        <v>616</v>
+      </c>
+      <c r="C82" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" t="s">
+        <v>289</v>
+      </c>
+      <c r="E82" t="s">
+        <v>617</v>
+      </c>
+      <c r="F82" t="s">
+        <v>285</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>619</v>
+      </c>
+      <c r="B83" t="s">
+        <v>620</v>
+      </c>
+      <c r="C83" t="s">
+        <v>210</v>
+      </c>
+      <c r="D83" t="s">
+        <v>452</v>
+      </c>
+      <c r="E83" t="s">
+        <v>621</v>
+      </c>
+      <c r="F83" t="s">
+        <v>525</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>623</v>
+      </c>
+      <c r="B84" t="s">
+        <v>624</v>
+      </c>
+      <c r="C84" t="s">
+        <v>295</v>
+      </c>
+      <c r="D84" t="s">
+        <v>452</v>
+      </c>
+      <c r="E84" t="s">
+        <v>625</v>
+      </c>
+      <c r="F84" t="s">
+        <v>626</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>628</v>
+      </c>
+      <c r="B85" t="s">
+        <v>629</v>
+      </c>
+      <c r="C85" t="s">
+        <v>581</v>
+      </c>
+      <c r="D85" t="s">
+        <v>223</v>
+      </c>
+      <c r="E85" t="s">
+        <v>630</v>
+      </c>
+      <c r="F85" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>632</v>
+      </c>
+      <c r="B86" t="s">
+        <v>633</v>
+      </c>
+      <c r="C86" t="s">
+        <v>634</v>
+      </c>
+      <c r="D86" t="s">
+        <v>223</v>
+      </c>
+      <c r="E86" t="s">
+        <v>635</v>
+      </c>
+      <c r="F86" t="s">
+        <v>636</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>638</v>
+      </c>
+      <c r="B87" t="s">
+        <v>639</v>
+      </c>
+      <c r="C87" t="s">
+        <v>581</v>
+      </c>
+      <c r="D87" t="s">
+        <v>223</v>
+      </c>
+      <c r="E87" t="s">
+        <v>640</v>
+      </c>
+      <c r="F87" t="s">
+        <v>641</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>643</v>
+      </c>
+      <c r="B88" t="s">
+        <v>560</v>
+      </c>
+      <c r="C88" t="s">
+        <v>264</v>
+      </c>
+      <c r="D88" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" t="s">
+        <v>561</v>
+      </c>
+      <c r="F88" t="s">
+        <v>562</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>645</v>
+      </c>
+      <c r="B89" t="s">
+        <v>646</v>
+      </c>
+      <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" t="s">
+        <v>223</v>
+      </c>
+      <c r="E89" t="s">
+        <v>647</v>
+      </c>
+      <c r="F89" t="s">
+        <v>648</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>650</v>
+      </c>
+      <c r="B90" t="s">
+        <v>651</v>
+      </c>
+      <c r="C90" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" t="s">
+        <v>223</v>
+      </c>
+      <c r="E90" t="s">
+        <v>230</v>
+      </c>
+      <c r="F90" t="s">
+        <v>552</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>653</v>
+      </c>
+      <c r="B91" t="s">
+        <v>654</v>
+      </c>
+      <c r="C91" t="s">
+        <v>634</v>
+      </c>
+      <c r="D91" t="s">
+        <v>223</v>
+      </c>
+      <c r="E91" t="s">
+        <v>655</v>
+      </c>
+      <c r="F91" t="s">
+        <v>656</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>658</v>
+      </c>
+      <c r="B92" t="s">
+        <v>659</v>
+      </c>
+      <c r="C92" t="s">
+        <v>660</v>
+      </c>
+      <c r="D92" t="s">
+        <v>223</v>
+      </c>
+      <c r="E92" t="s">
+        <v>661</v>
+      </c>
+      <c r="F92" t="s">
+        <v>285</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>663</v>
+      </c>
+      <c r="B93" t="s">
+        <v>664</v>
+      </c>
+      <c r="C93" t="s">
+        <v>210</v>
+      </c>
+      <c r="D93" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" t="s">
+        <v>665</v>
+      </c>
+      <c r="F93" t="s">
+        <v>255</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>667</v>
+      </c>
+      <c r="B94" t="s">
+        <v>263</v>
+      </c>
+      <c r="C94" t="s">
+        <v>264</v>
+      </c>
+      <c r="D94" t="s">
+        <v>223</v>
+      </c>
+      <c r="E94" t="s">
+        <v>668</v>
+      </c>
+      <c r="F94" t="s">
+        <v>43</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>670</v>
+      </c>
+      <c r="B95" t="s">
+        <v>408</v>
+      </c>
+      <c r="C95" t="s">
+        <v>264</v>
+      </c>
+      <c r="D95" t="s">
+        <v>223</v>
+      </c>
+      <c r="E95" t="s">
+        <v>671</v>
+      </c>
+      <c r="F95" t="s">
+        <v>271</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>673</v>
+      </c>
+      <c r="B96" t="s">
+        <v>674</v>
+      </c>
+      <c r="C96" t="s">
+        <v>259</v>
+      </c>
+      <c r="D96" t="s">
+        <v>302</v>
+      </c>
+      <c r="E96" t="s">
+        <v>675</v>
+      </c>
+      <c r="F96" t="s">
+        <v>676</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>678</v>
+      </c>
+      <c r="B97" t="s">
+        <v>679</v>
+      </c>
+      <c r="C97" t="s">
+        <v>680</v>
+      </c>
+      <c r="D97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E97" t="s">
+        <v>681</v>
+      </c>
+      <c r="F97" t="s">
+        <v>682</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>684</v>
+      </c>
+      <c r="B98" t="s">
+        <v>685</v>
+      </c>
+      <c r="C98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D98" t="s">
+        <v>223</v>
+      </c>
+      <c r="E98" t="s">
+        <v>686</v>
+      </c>
+      <c r="F98" t="s">
+        <v>687</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>684</v>
+      </c>
+      <c r="B99" t="s">
+        <v>685</v>
+      </c>
+      <c r="C99" t="s">
+        <v>259</v>
+      </c>
+      <c r="D99" t="s">
+        <v>223</v>
+      </c>
+      <c r="E99" t="s">
+        <v>689</v>
+      </c>
+      <c r="F99" t="s">
+        <v>687</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>691</v>
+      </c>
+      <c r="B100" t="s">
+        <v>692</v>
+      </c>
+      <c r="C100" t="s">
+        <v>353</v>
+      </c>
+      <c r="D100" t="s">
+        <v>223</v>
+      </c>
+      <c r="E100" t="s">
+        <v>693</v>
+      </c>
+      <c r="F100" t="s">
+        <v>694</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>696</v>
+      </c>
+      <c r="B101" t="s">
+        <v>697</v>
+      </c>
+      <c r="C101" t="s">
+        <v>269</v>
+      </c>
+      <c r="D101" t="s">
+        <v>223</v>
+      </c>
+      <c r="E101" t="s">
+        <v>698</v>
+      </c>
+      <c r="F101" t="s">
+        <v>699</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>701</v>
+      </c>
+      <c r="B102" t="s">
+        <v>702</v>
+      </c>
+      <c r="C102" t="s">
+        <v>634</v>
+      </c>
+      <c r="D102" t="s">
+        <v>223</v>
+      </c>
+      <c r="E102" t="s">
+        <v>703</v>
+      </c>
+      <c r="F102" t="s">
+        <v>704</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>706</v>
+      </c>
+      <c r="B103" t="s">
+        <v>707</v>
+      </c>
+      <c r="C103" t="s">
+        <v>708</v>
+      </c>
+      <c r="D103" t="s">
+        <v>223</v>
+      </c>
+      <c r="E103" t="s">
+        <v>661</v>
+      </c>
+      <c r="F103" t="s">
+        <v>43</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>710</v>
+      </c>
+      <c r="B104" t="s">
+        <v>711</v>
+      </c>
+      <c r="C104" t="s">
+        <v>259</v>
+      </c>
+      <c r="D104" t="s">
+        <v>223</v>
+      </c>
+      <c r="E104" t="s">
+        <v>712</v>
+      </c>
+      <c r="F104" t="s">
+        <v>713</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>715</v>
+      </c>
+      <c r="B105" t="s">
+        <v>716</v>
+      </c>
+      <c r="C105" t="s">
+        <v>264</v>
+      </c>
+      <c r="D105" t="s">
+        <v>223</v>
+      </c>
+      <c r="E105" t="s">
+        <v>717</v>
+      </c>
+      <c r="F105" t="s">
+        <v>718</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>720</v>
+      </c>
+      <c r="B106" t="s">
+        <v>560</v>
+      </c>
+      <c r="C106" t="s">
+        <v>264</v>
+      </c>
+      <c r="D106" t="s">
+        <v>223</v>
+      </c>
+      <c r="E106" t="s">
+        <v>561</v>
+      </c>
+      <c r="F106" t="s">
+        <v>562</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>722</v>
+      </c>
+      <c r="B107" t="s">
+        <v>560</v>
+      </c>
+      <c r="C107" t="s">
+        <v>264</v>
+      </c>
+      <c r="D107" t="s">
+        <v>223</v>
+      </c>
+      <c r="E107" t="s">
+        <v>561</v>
+      </c>
+      <c r="F107" t="s">
+        <v>562</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>724</v>
+      </c>
+      <c r="B108" t="s">
+        <v>725</v>
+      </c>
+      <c r="C108" t="s">
+        <v>726</v>
+      </c>
+      <c r="D108" t="s">
+        <v>223</v>
+      </c>
+      <c r="E108" t="s">
+        <v>727</v>
+      </c>
+      <c r="F108" t="s">
+        <v>341</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>729</v>
+      </c>
+      <c r="B109" t="s">
+        <v>263</v>
+      </c>
+      <c r="C109" t="s">
+        <v>730</v>
+      </c>
+      <c r="D109" t="s">
+        <v>223</v>
+      </c>
+      <c r="E109" t="s">
+        <v>731</v>
+      </c>
+      <c r="F109" t="s">
+        <v>43</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>733</v>
+      </c>
+      <c r="B110" t="s">
+        <v>734</v>
+      </c>
+      <c r="C110" t="s">
+        <v>254</v>
+      </c>
+      <c r="D110" t="s">
+        <v>452</v>
+      </c>
+      <c r="E110" t="s">
+        <v>735</v>
+      </c>
+      <c r="F110" t="s">
+        <v>736</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>738</v>
+      </c>
+      <c r="B111" t="s">
+        <v>739</v>
+      </c>
+      <c r="C111" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" t="s">
+        <v>223</v>
+      </c>
+      <c r="E111" t="s">
+        <v>740</v>
+      </c>
+      <c r="F111" t="s">
+        <v>43</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>742</v>
+      </c>
+      <c r="B112" t="s">
+        <v>743</v>
+      </c>
+      <c r="C112" t="s">
+        <v>744</v>
+      </c>
+      <c r="D112" t="s">
+        <v>289</v>
+      </c>
+      <c r="E112" t="s">
+        <v>745</v>
+      </c>
+      <c r="F112" t="s">
+        <v>746</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>748</v>
+      </c>
+      <c r="B113" t="s">
+        <v>749</v>
+      </c>
+      <c r="C113" t="s">
+        <v>750</v>
+      </c>
+      <c r="D113" t="s">
+        <v>223</v>
+      </c>
+      <c r="E113" t="s">
+        <v>751</v>
+      </c>
+      <c r="F113" t="s">
+        <v>43</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>753</v>
+      </c>
+      <c r="B114" t="s">
+        <v>246</v>
+      </c>
+      <c r="C114" t="s">
+        <v>247</v>
+      </c>
+      <c r="D114" t="s">
+        <v>223</v>
+      </c>
+      <c r="E114" t="s">
+        <v>754</v>
+      </c>
+      <c r="F114" t="s">
+        <v>43</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>756</v>
+      </c>
+      <c r="B115" t="s">
+        <v>757</v>
+      </c>
+      <c r="C115" t="s">
+        <v>259</v>
+      </c>
+      <c r="D115" t="s">
+        <v>289</v>
+      </c>
+      <c r="E115" t="s">
+        <v>758</v>
+      </c>
+      <c r="F115" t="s">
+        <v>759</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>761</v>
+      </c>
+      <c r="B116" t="s">
+        <v>762</v>
+      </c>
+      <c r="C116" t="s">
+        <v>431</v>
+      </c>
+      <c r="D116" t="s">
+        <v>289</v>
+      </c>
+      <c r="E116" t="s">
+        <v>763</v>
+      </c>
+      <c r="F116" t="s">
+        <v>420</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>765</v>
+      </c>
+      <c r="B117" t="s">
+        <v>766</v>
+      </c>
+      <c r="C117" t="s">
+        <v>325</v>
+      </c>
+      <c r="D117" t="s">
+        <v>289</v>
+      </c>
+      <c r="E117" t="s">
+        <v>767</v>
+      </c>
+      <c r="F117" t="s">
+        <v>768</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>770</v>
+      </c>
+      <c r="B118" t="s">
+        <v>771</v>
+      </c>
+      <c r="C118" t="s">
+        <v>772</v>
+      </c>
+      <c r="D118" t="s">
+        <v>223</v>
+      </c>
+      <c r="E118" t="s">
+        <v>773</v>
+      </c>
+      <c r="F118" t="s">
+        <v>774</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>776</v>
+      </c>
+      <c r="B119" t="s">
+        <v>777</v>
+      </c>
+      <c r="C119" t="s">
+        <v>778</v>
+      </c>
+      <c r="D119" t="s">
+        <v>223</v>
+      </c>
+      <c r="E119" t="s">
+        <v>779</v>
+      </c>
+      <c r="F119" t="s">
+        <v>780</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>782</v>
+      </c>
+      <c r="B120" t="s">
+        <v>783</v>
+      </c>
+      <c r="C120" t="s">
+        <v>784</v>
+      </c>
+      <c r="D120" t="s">
+        <v>302</v>
+      </c>
+      <c r="E120" t="s">
+        <v>785</v>
+      </c>
+      <c r="F120" t="s">
+        <v>786</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>788</v>
+      </c>
+      <c r="B121" t="s">
+        <v>674</v>
+      </c>
+      <c r="C121" t="s">
+        <v>259</v>
+      </c>
+      <c r="D121" t="s">
+        <v>302</v>
+      </c>
+      <c r="E121" t="s">
+        <v>675</v>
+      </c>
+      <c r="F121" t="s">
+        <v>676</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>790</v>
+      </c>
+      <c r="B122" t="s">
+        <v>791</v>
+      </c>
+      <c r="C122" t="s">
+        <v>210</v>
+      </c>
+      <c r="D122" t="s">
+        <v>223</v>
+      </c>
+      <c r="E122" t="s">
+        <v>792</v>
+      </c>
+      <c r="F122" t="s">
+        <v>626</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>794</v>
+      </c>
+      <c r="B123" t="s">
+        <v>795</v>
+      </c>
+      <c r="C123" t="s">
+        <v>796</v>
+      </c>
+      <c r="D123" t="s">
+        <v>223</v>
+      </c>
+      <c r="E123" t="s">
+        <v>797</v>
+      </c>
+      <c r="F123" t="s">
+        <v>798</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>800</v>
+      </c>
+      <c r="B124" t="s">
+        <v>483</v>
+      </c>
+      <c r="C124" t="s">
+        <v>801</v>
+      </c>
+      <c r="D124" t="s">
+        <v>302</v>
+      </c>
+      <c r="E124" t="s">
+        <v>802</v>
+      </c>
+      <c r="F124" t="s">
+        <v>803</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>805</v>
+      </c>
+      <c r="B125" t="s">
+        <v>806</v>
+      </c>
+      <c r="C125" t="s">
+        <v>210</v>
+      </c>
+      <c r="D125" t="s">
+        <v>289</v>
+      </c>
+      <c r="E125" t="s">
+        <v>807</v>
+      </c>
+      <c r="F125" t="s">
+        <v>808</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>810</v>
+      </c>
+      <c r="B126" t="s">
+        <v>791</v>
+      </c>
+      <c r="C126" t="s">
+        <v>264</v>
+      </c>
+      <c r="D126" t="s">
+        <v>223</v>
+      </c>
+      <c r="E126" t="s">
+        <v>811</v>
+      </c>
+      <c r="F126" t="s">
+        <v>626</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>813</v>
+      </c>
+      <c r="B127" t="s">
+        <v>300</v>
+      </c>
+      <c r="C127" t="s">
+        <v>301</v>
+      </c>
+      <c r="D127" t="s">
+        <v>223</v>
+      </c>
+      <c r="E127" t="s">
+        <v>303</v>
+      </c>
+      <c r="F127" t="s">
+        <v>43</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>815</v>
+      </c>
+      <c r="B128" t="s">
+        <v>816</v>
+      </c>
+      <c r="C128" t="s">
+        <v>259</v>
+      </c>
+      <c r="D128" t="s">
+        <v>223</v>
+      </c>
+      <c r="E128" t="s">
+        <v>635</v>
+      </c>
+      <c r="F128" t="s">
+        <v>817</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>819</v>
+      </c>
+      <c r="B129" t="s">
+        <v>820</v>
+      </c>
+      <c r="C129" t="s">
+        <v>821</v>
+      </c>
+      <c r="D129" t="s">
+        <v>223</v>
+      </c>
+      <c r="E129" t="s">
+        <v>43</v>
+      </c>
+      <c r="F129" t="s">
+        <v>768</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>823</v>
+      </c>
+      <c r="B130" t="s">
+        <v>824</v>
+      </c>
+      <c r="C130" t="s">
+        <v>825</v>
+      </c>
+      <c r="D130" t="s">
+        <v>223</v>
+      </c>
+      <c r="E130" t="s">
+        <v>826</v>
+      </c>
+      <c r="F130" t="s">
+        <v>43</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>828</v>
+      </c>
+      <c r="B131" t="s">
+        <v>829</v>
+      </c>
+      <c r="C131" t="s">
+        <v>830</v>
+      </c>
+      <c r="D131" t="s">
+        <v>223</v>
+      </c>
+      <c r="E131" t="s">
+        <v>831</v>
+      </c>
+      <c r="F131" t="s">
+        <v>43</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>833</v>
+      </c>
+      <c r="B132" t="s">
+        <v>234</v>
+      </c>
+      <c r="C132" t="s">
+        <v>210</v>
+      </c>
+      <c r="D132" t="s">
+        <v>223</v>
+      </c>
+      <c r="E132" t="s">
+        <v>378</v>
+      </c>
+      <c r="F132" t="s">
+        <v>236</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>835</v>
+      </c>
+      <c r="B133" t="s">
+        <v>234</v>
+      </c>
+      <c r="C133" t="s">
+        <v>210</v>
+      </c>
+      <c r="D133" t="s">
+        <v>223</v>
+      </c>
+      <c r="E133" t="s">
+        <v>836</v>
+      </c>
+      <c r="F133" t="s">
+        <v>43</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>838</v>
+      </c>
+      <c r="B134" t="s">
+        <v>839</v>
+      </c>
+      <c r="C134" t="s">
+        <v>840</v>
+      </c>
+      <c r="D134" t="s">
+        <v>223</v>
+      </c>
+      <c r="E134" t="s">
+        <v>841</v>
+      </c>
+      <c r="F134" t="s">
+        <v>842</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>844</v>
+      </c>
+      <c r="B135" t="s">
+        <v>845</v>
+      </c>
+      <c r="C135" t="s">
+        <v>210</v>
+      </c>
+      <c r="D135" t="s">
+        <v>223</v>
+      </c>
+      <c r="E135" t="s">
+        <v>846</v>
+      </c>
+      <c r="F135" t="s">
+        <v>847</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>849</v>
+      </c>
+      <c r="B136" t="s">
+        <v>850</v>
+      </c>
+      <c r="C136" t="s">
+        <v>259</v>
+      </c>
+      <c r="D136" t="s">
+        <v>223</v>
+      </c>
+      <c r="E136" t="s">
+        <v>851</v>
+      </c>
+      <c r="F136" t="s">
+        <v>852</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>854</v>
+      </c>
+      <c r="B137" t="s">
+        <v>855</v>
+      </c>
+      <c r="C137" t="s">
+        <v>856</v>
+      </c>
+      <c r="D137" t="s">
+        <v>223</v>
+      </c>
+      <c r="E137" t="s">
+        <v>661</v>
+      </c>
+      <c r="F137" t="s">
+        <v>857</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>859</v>
+      </c>
+      <c r="B138" t="s">
+        <v>860</v>
+      </c>
+      <c r="C138" t="s">
+        <v>264</v>
+      </c>
+      <c r="D138" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138" t="s">
+        <v>861</v>
+      </c>
+      <c r="F138" t="s">
+        <v>525</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>863</v>
+      </c>
+      <c r="B139" t="s">
+        <v>864</v>
+      </c>
+      <c r="C139" t="s">
+        <v>865</v>
+      </c>
+      <c r="D139" t="s">
+        <v>223</v>
+      </c>
+      <c r="E139" t="s">
+        <v>866</v>
+      </c>
+      <c r="F139" t="s">
+        <v>746</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>868</v>
+      </c>
+      <c r="B140" t="s">
+        <v>869</v>
+      </c>
+      <c r="C140" t="s">
+        <v>870</v>
+      </c>
+      <c r="D140" t="s">
+        <v>223</v>
+      </c>
+      <c r="E140" t="s">
+        <v>871</v>
+      </c>
+      <c r="F140" t="s">
+        <v>613</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>873</v>
+      </c>
+      <c r="B141" t="s">
+        <v>874</v>
+      </c>
+      <c r="C141" t="s">
+        <v>264</v>
+      </c>
+      <c r="D141" t="s">
+        <v>223</v>
+      </c>
+      <c r="E141" t="s">
+        <v>875</v>
+      </c>
+      <c r="F141" t="s">
+        <v>876</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>878</v>
+      </c>
+      <c r="B142" t="s">
+        <v>560</v>
+      </c>
+      <c r="C142" t="s">
+        <v>264</v>
+      </c>
+      <c r="D142" t="s">
+        <v>223</v>
+      </c>
+      <c r="E142" t="s">
+        <v>879</v>
+      </c>
+      <c r="F142" t="s">
+        <v>562</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>881</v>
+      </c>
+      <c r="B143" t="s">
+        <v>294</v>
+      </c>
+      <c r="C143" t="s">
+        <v>259</v>
+      </c>
+      <c r="D143" t="s">
+        <v>223</v>
+      </c>
+      <c r="E143" t="s">
+        <v>882</v>
+      </c>
+      <c r="F143" t="s">
+        <v>43</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>884</v>
+      </c>
+      <c r="B144" t="s">
+        <v>885</v>
+      </c>
+      <c r="C144" t="s">
+        <v>750</v>
+      </c>
+      <c r="D144" t="s">
+        <v>223</v>
+      </c>
+      <c r="E144" t="s">
+        <v>886</v>
+      </c>
+      <c r="F144" t="s">
+        <v>887</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>884</v>
+      </c>
+      <c r="B145" t="s">
+        <v>889</v>
+      </c>
+      <c r="C145" t="s">
+        <v>210</v>
+      </c>
+      <c r="D145" t="s">
+        <v>223</v>
+      </c>
+      <c r="E145" t="s">
+        <v>890</v>
+      </c>
+      <c r="F145" t="s">
+        <v>891</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>893</v>
+      </c>
+      <c r="B146" t="s">
+        <v>894</v>
+      </c>
+      <c r="C146" t="s">
+        <v>247</v>
+      </c>
+      <c r="D146" t="s">
+        <v>302</v>
+      </c>
+      <c r="E146" t="s">
+        <v>895</v>
+      </c>
+      <c r="F146" t="s">
+        <v>896</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>898</v>
+      </c>
+      <c r="B147" t="s">
+        <v>899</v>
+      </c>
+      <c r="C147" t="s">
+        <v>900</v>
+      </c>
+      <c r="D147" t="s">
+        <v>223</v>
+      </c>
+      <c r="E147" t="s">
+        <v>901</v>
+      </c>
+      <c r="F147" t="s">
+        <v>902</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>904</v>
+      </c>
+      <c r="B148" t="s">
+        <v>697</v>
+      </c>
+      <c r="C148" t="s">
+        <v>269</v>
+      </c>
+      <c r="D148" t="s">
+        <v>223</v>
+      </c>
+      <c r="E148" t="s">
+        <v>698</v>
+      </c>
+      <c r="F148" t="s">
+        <v>699</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>906</v>
+      </c>
+      <c r="B149" t="s">
+        <v>907</v>
+      </c>
+      <c r="C149" t="s">
+        <v>353</v>
+      </c>
+      <c r="D149" t="s">
+        <v>223</v>
+      </c>
+      <c r="E149" t="s">
+        <v>908</v>
+      </c>
+      <c r="F149" t="s">
+        <v>43</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>910</v>
+      </c>
+      <c r="B150" t="s">
+        <v>911</v>
+      </c>
+      <c r="C150" t="s">
+        <v>912</v>
+      </c>
+      <c r="D150" t="s">
+        <v>223</v>
+      </c>
+      <c r="E150" t="s">
+        <v>913</v>
+      </c>
+      <c r="F150" t="s">
+        <v>914</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>916</v>
+      </c>
+      <c r="B151" t="s">
+        <v>917</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>223</v>
+      </c>
+      <c r="E151" t="s">
+        <v>918</v>
+      </c>
+      <c r="F151" t="s">
+        <v>919</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -3536,6 +8324,119 @@
     <hyperlink ref="H36" r:id="rId35"/>
     <hyperlink ref="H37" r:id="rId36"/>
     <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3544,7 +8445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3583,8 +8484,1258 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C2" t="s">
+        <v>923</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>924</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>926</v>
+      </c>
+      <c r="B3" t="s">
+        <v>927</v>
+      </c>
+      <c r="C3" t="s">
+        <v>928</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>929</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>931</v>
+      </c>
+      <c r="B4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C4" t="s">
+        <v>933</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>934</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>936</v>
+      </c>
+      <c r="B5" t="s">
+        <v>937</v>
+      </c>
+      <c r="C5" t="s">
+        <v>938</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>924</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>940</v>
+      </c>
+      <c r="B6" t="s">
+        <v>941</v>
+      </c>
+      <c r="C6" t="s">
+        <v>942</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>924</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>944</v>
+      </c>
+      <c r="B7" t="s">
+        <v>945</v>
+      </c>
+      <c r="C7" t="s">
+        <v>946</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>947</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>949</v>
+      </c>
+      <c r="B8" t="s">
+        <v>950</v>
+      </c>
+      <c r="C8" t="s">
+        <v>951</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>929</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>953</v>
+      </c>
+      <c r="B9" t="s">
+        <v>954</v>
+      </c>
+      <c r="C9" t="s">
+        <v>955</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>929</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>957</v>
+      </c>
+      <c r="B10" t="s">
+        <v>958</v>
+      </c>
+      <c r="C10" t="s">
+        <v>959</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>934</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>961</v>
+      </c>
+      <c r="B11" t="s">
+        <v>962</v>
+      </c>
+      <c r="C11" t="s">
+        <v>963</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>924</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>965</v>
+      </c>
+      <c r="B12" t="s">
+        <v>966</v>
+      </c>
+      <c r="C12" t="s">
+        <v>967</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>968</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>970</v>
+      </c>
+      <c r="B13" t="s">
+        <v>971</v>
+      </c>
+      <c r="C13" t="s">
+        <v>933</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>972</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>974</v>
+      </c>
+      <c r="B14" t="s">
+        <v>975</v>
+      </c>
+      <c r="C14" t="s">
+        <v>976</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>934</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>978</v>
+      </c>
+      <c r="B15" t="s">
+        <v>979</v>
+      </c>
+      <c r="C15" t="s">
+        <v>980</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>924</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>982</v>
+      </c>
+      <c r="B16" t="s">
+        <v>983</v>
+      </c>
+      <c r="C16" t="s">
+        <v>933</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>984</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>982</v>
+      </c>
+      <c r="B17" t="s">
+        <v>986</v>
+      </c>
+      <c r="C17" t="s">
+        <v>987</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>929</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>989</v>
+      </c>
+      <c r="B18" t="s">
+        <v>990</v>
+      </c>
+      <c r="C18" t="s">
+        <v>933</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>992</v>
+      </c>
+      <c r="B19" t="s">
+        <v>993</v>
+      </c>
+      <c r="C19" t="s">
+        <v>994</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>968</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>996</v>
+      </c>
+      <c r="B20" t="s">
+        <v>997</v>
+      </c>
+      <c r="C20" t="s">
+        <v>998</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>924</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C21" t="s">
+        <v>933</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>579</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>924</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C24" t="s">
+        <v>928</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>924</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
+        <v>924</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C26" t="s">
+        <v>388</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" t="s">
+        <v>924</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>984</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" t="s">
+        <v>947</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s">
+        <v>924</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" t="s">
+        <v>934</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" t="s">
+        <v>924</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" t="s">
+        <v>924</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C35" t="s">
+        <v>933</v>
+      </c>
+      <c r="D35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" t="s">
+        <v>984</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C36" t="s">
+        <v>264</v>
+      </c>
+      <c r="D36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" t="s">
+        <v>924</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C39" t="s">
+        <v>933</v>
+      </c>
+      <c r="D39" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D40" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" t="s">
+        <v>924</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C41" t="s">
+        <v>933</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" t="s">
+        <v>924</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D42" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" t="s">
+        <v>984</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" t="s">
+        <v>968</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" t="s">
+        <v>929</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D45" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" t="s">
+        <v>924</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B46" t="s">
+        <v>971</v>
+      </c>
+      <c r="C46" t="s">
+        <v>933</v>
+      </c>
+      <c r="D46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D47" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" t="s">
+        <v>929</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D49" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" t="s">
+        <v>929</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50" t="s">
+        <v>924</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>388</v>
+      </c>
+      <c r="D51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51" t="s">
+        <v>924</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" t="s">
+        <v>934</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D53" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" t="s">
+        <v>924</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-08-18.xlsx
+++ b/docs/xlsx/jobs-2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1147">
   <si>
     <t>Title</t>
   </si>
@@ -1873,6 +1873,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b94ac9f2cd9b44a38f54c13e8d06eaaa-finance-operations-manager-future-roots-inc-dublab-los-angeles</t>
   </si>
   <si>
+    <t>Finance and Admin, Officer</t>
+  </si>
+  <si>
+    <t>Ground Zero</t>
+  </si>
+  <si>
+    <t>Agartala, Agartala, IN</t>
+  </si>
+  <si>
+    <t>INR 600000.00 - 800000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d55985b7d4754cc6b1d7494cb07dae1b-finance-and-admin-officer-ground-zero-agartala</t>
+  </si>
+  <si>
     <t>Freelancer International Fundraiser</t>
   </si>
   <si>
@@ -1945,6 +1963,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/889e6cfe814745e7a8a76fc62cf252cd-hellman-and-simons-fellow-for-science-engineering-and-technology-american-academy-of-arts-and-sciences-cambridge</t>
   </si>
   <si>
+    <t>High School Math Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25e558bd5b0143f4b65f3b35ee66aa45-high-school-math-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
+    <t>High School Science Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5bc9eab311b40809dd0284c77898efd-high-school-science-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
     <t>High School Special Education Teacher</t>
   </si>
   <si>
@@ -1960,9 +1990,6 @@
     <t>USD 85000.00 - 93000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/643d53ad701744b2866da0a33469319a-housing-attorney-nmic-northern-manhattan-improvement-corporation-new-york</t>
   </si>
   <si>
@@ -2035,6 +2062,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/1be7389458ee4f898b3d302c0bcb6b6e-investigator-trial-office-citywide-the-legal-aid-society-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Lead - Fundraising and Donor Management, Mumbai</t>
+  </si>
+  <si>
+    <t>Mumbai, Mumbai, IN</t>
+  </si>
+  <si>
+    <t>USD 2400000.00 - 2500000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55b488e3f2174b1ba49e9e9cc5e92976-lead-fundraising-and-donor-management-mumbai-ground-zero-mumbai</t>
+  </si>
+  <si>
     <t>Legal Fellowship</t>
   </si>
   <si>
@@ -2068,6 +2107,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/13408098ff4d40f995f4d2d41c4464ed-literacy-specialist-literacy-new-jersey-kearny</t>
   </si>
   <si>
+    <t>Manager- CSR &amp; Social Impact Programs, Gurugram</t>
+  </si>
+  <si>
+    <t>Gurugram, Gurugram, IN</t>
+  </si>
+  <si>
+    <t>INR 800000.00 - 1000000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f36bbdc491f42529b39e27771c8b888-manager-csr-social-impact-programs-gurugram-ground-zero-gurugram</t>
+  </si>
+  <si>
     <t>Manager, Direct Marketing</t>
   </si>
   <si>
@@ -2176,6 +2227,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/b93e822986e549e4bdf91ed4755a0de1-membership-specialist-the-science-friday-initiative-new-york</t>
   </si>
   <si>
+    <t>Middle School Math Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3309dd2160cd43db8abaa2593bfe115c-middle-school-math-teacher-uncommon-schools-new-york</t>
+  </si>
+  <si>
     <t>Middle School Science Teacher</t>
   </si>
   <si>
@@ -2563,6 +2620,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/60086526a6be46c98cfd43258d70e5ca-senior-program-officer-pride-foundation-seattle</t>
   </si>
   <si>
+    <t>Senior Specialist – Curriculum [Education], Ranchi Ranchi, Jharkhand, India Managed by Ground Zero</t>
+  </si>
+  <si>
+    <t>Ranchi, Ranchi, IN</t>
+  </si>
+  <si>
+    <t>INR 1000000.00 - 1400000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80fd7336fe9b4f0cad5560c4f99b1f47-senior-specialist-curriculum-education-ranchi-ranchi-jharkhand-india-managed-by-ground-zero-ground-zero-ranchi</t>
+  </si>
+  <si>
     <t>Senior Technical Editor</t>
   </si>
   <si>
@@ -2732,6 +2801,18 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/21a704212ddc4017bccfe7e8abdd708d-staff-attorney-ii-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>State Numeracy Specialist, New Delhi</t>
+  </si>
+  <si>
+    <t>New Delhi, New Delhi, IN</t>
+  </si>
+  <si>
+    <t>INR 1000000.00 - 1200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0c86874b2044430b71631d84d83a443-state-numeracy-specialist-new-delhi-ground-zero-new-delhi</t>
   </si>
   <si>
     <t>Supervising Staff Attorney, Immigration</t>
@@ -4795,7 +4876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -6705,85 +6786,85 @@
         <v>620</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>621</v>
       </c>
       <c r="D83" t="s">
-        <v>452</v>
+        <v>223</v>
       </c>
       <c r="E83" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F83" t="s">
-        <v>525</v>
+        <v>623</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B84" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C84" t="s">
-        <v>295</v>
+        <v>210</v>
       </c>
       <c r="D84" t="s">
         <v>452</v>
       </c>
       <c r="E84" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F84" t="s">
-        <v>626</v>
+        <v>525</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C85" t="s">
-        <v>581</v>
+        <v>295</v>
       </c>
       <c r="D85" t="s">
-        <v>223</v>
+        <v>452</v>
       </c>
       <c r="E85" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F85" t="s">
-        <v>43</v>
+        <v>632</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B86" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C86" t="s">
-        <v>634</v>
+        <v>581</v>
       </c>
       <c r="D86" t="s">
         <v>223</v>
       </c>
       <c r="E86" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F86" t="s">
-        <v>636</v>
+        <v>43</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>637</v>
@@ -6797,50 +6878,50 @@
         <v>639</v>
       </c>
       <c r="C87" t="s">
-        <v>581</v>
+        <v>640</v>
       </c>
       <c r="D87" t="s">
         <v>223</v>
       </c>
       <c r="E87" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F87" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B88" t="s">
-        <v>560</v>
+        <v>645</v>
       </c>
       <c r="C88" t="s">
-        <v>264</v>
+        <v>581</v>
       </c>
       <c r="D88" t="s">
         <v>223</v>
       </c>
       <c r="E88" t="s">
-        <v>561</v>
+        <v>646</v>
       </c>
       <c r="F88" t="s">
-        <v>562</v>
+        <v>647</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B89" t="s">
-        <v>646</v>
+        <v>560</v>
       </c>
       <c r="C89" t="s">
         <v>264</v>
@@ -6849,21 +6930,21 @@
         <v>223</v>
       </c>
       <c r="E89" t="s">
-        <v>647</v>
+        <v>561</v>
       </c>
       <c r="F89" t="s">
-        <v>648</v>
+        <v>562</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B90" t="s">
-        <v>651</v>
+        <v>560</v>
       </c>
       <c r="C90" t="s">
         <v>264</v>
@@ -6872,10 +6953,10 @@
         <v>223</v>
       </c>
       <c r="E90" t="s">
-        <v>230</v>
+        <v>561</v>
       </c>
       <c r="F90" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>652</v>
@@ -6886,168 +6967,168 @@
         <v>653</v>
       </c>
       <c r="B91" t="s">
+        <v>560</v>
+      </c>
+      <c r="C91" t="s">
+        <v>264</v>
+      </c>
+      <c r="D91" t="s">
+        <v>223</v>
+      </c>
+      <c r="E91" t="s">
+        <v>561</v>
+      </c>
+      <c r="F91" t="s">
+        <v>562</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="C91" t="s">
-        <v>634</v>
-      </c>
-      <c r="D91" t="s">
-        <v>223</v>
-      </c>
-      <c r="E91" t="s">
-        <v>655</v>
-      </c>
-      <c r="F91" t="s">
-        <v>656</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>655</v>
+      </c>
+      <c r="B92" t="s">
+        <v>656</v>
+      </c>
+      <c r="C92" t="s">
+        <v>264</v>
+      </c>
+      <c r="D92" t="s">
+        <v>223</v>
+      </c>
+      <c r="E92" t="s">
+        <v>657</v>
+      </c>
+      <c r="F92" t="s">
+        <v>623</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="B92" t="s">
-        <v>659</v>
-      </c>
-      <c r="C92" t="s">
-        <v>660</v>
-      </c>
-      <c r="D92" t="s">
-        <v>223</v>
-      </c>
-      <c r="E92" t="s">
-        <v>661</v>
-      </c>
-      <c r="F92" t="s">
-        <v>285</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C93" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="D93" t="s">
         <v>223</v>
       </c>
       <c r="E93" t="s">
-        <v>665</v>
+        <v>230</v>
       </c>
       <c r="F93" t="s">
-        <v>255</v>
+        <v>552</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B94" t="s">
-        <v>263</v>
+        <v>663</v>
       </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>640</v>
       </c>
       <c r="D94" t="s">
         <v>223</v>
       </c>
       <c r="E94" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="F94" t="s">
-        <v>43</v>
+        <v>665</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>667</v>
+      </c>
+      <c r="B95" t="s">
+        <v>668</v>
+      </c>
+      <c r="C95" t="s">
+        <v>669</v>
+      </c>
+      <c r="D95" t="s">
+        <v>223</v>
+      </c>
+      <c r="E95" t="s">
         <v>670</v>
       </c>
-      <c r="B95" t="s">
-        <v>408</v>
-      </c>
-      <c r="C95" t="s">
-        <v>264</v>
-      </c>
-      <c r="D95" t="s">
-        <v>223</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
+        <v>285</v>
+      </c>
+      <c r="H95" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="F95" t="s">
-        <v>271</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>672</v>
+      </c>
+      <c r="B96" t="s">
         <v>673</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>210</v>
+      </c>
+      <c r="D96" t="s">
+        <v>223</v>
+      </c>
+      <c r="E96" t="s">
         <v>674</v>
       </c>
-      <c r="C96" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" t="s">
-        <v>302</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>255</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="F96" t="s">
-        <v>676</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>676</v>
+      </c>
+      <c r="B97" t="s">
+        <v>263</v>
+      </c>
+      <c r="C97" t="s">
+        <v>264</v>
+      </c>
+      <c r="D97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E97" t="s">
+        <v>677</v>
+      </c>
+      <c r="F97" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="B97" t="s">
-        <v>679</v>
-      </c>
-      <c r="C97" t="s">
-        <v>680</v>
-      </c>
-      <c r="D97" t="s">
-        <v>223</v>
-      </c>
-      <c r="E97" t="s">
-        <v>681</v>
-      </c>
-      <c r="F97" t="s">
-        <v>682</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B98" t="s">
-        <v>685</v>
+        <v>408</v>
       </c>
       <c r="C98" t="s">
         <v>264</v>
@@ -7056,136 +7137,136 @@
         <v>223</v>
       </c>
       <c r="E98" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="F98" t="s">
-        <v>687</v>
+        <v>271</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>682</v>
+      </c>
+      <c r="B99" t="s">
+        <v>620</v>
+      </c>
+      <c r="C99" t="s">
+        <v>683</v>
+      </c>
+      <c r="D99" t="s">
+        <v>223</v>
+      </c>
+      <c r="E99" t="s">
         <v>684</v>
       </c>
-      <c r="B99" t="s">
+      <c r="F99" t="s">
+        <v>623</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="C99" t="s">
-        <v>259</v>
-      </c>
-      <c r="D99" t="s">
-        <v>223</v>
-      </c>
-      <c r="E99" t="s">
-        <v>689</v>
-      </c>
-      <c r="F99" t="s">
-        <v>687</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B100" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C100" t="s">
-        <v>353</v>
+        <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="E100" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="F100" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>691</v>
+      </c>
+      <c r="B101" t="s">
+        <v>692</v>
+      </c>
+      <c r="C101" t="s">
+        <v>693</v>
+      </c>
+      <c r="D101" t="s">
+        <v>223</v>
+      </c>
+      <c r="E101" t="s">
+        <v>694</v>
+      </c>
+      <c r="F101" t="s">
+        <v>695</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="B101" t="s">
-        <v>697</v>
-      </c>
-      <c r="C101" t="s">
-        <v>269</v>
-      </c>
-      <c r="D101" t="s">
-        <v>223</v>
-      </c>
-      <c r="E101" t="s">
-        <v>698</v>
-      </c>
-      <c r="F101" t="s">
-        <v>699</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B102" t="s">
-        <v>702</v>
+        <v>620</v>
       </c>
       <c r="C102" t="s">
-        <v>634</v>
+        <v>698</v>
       </c>
       <c r="D102" t="s">
         <v>223</v>
       </c>
       <c r="E102" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="F102" t="s">
-        <v>704</v>
+        <v>623</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="B103" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C103" t="s">
-        <v>708</v>
+        <v>264</v>
       </c>
       <c r="D103" t="s">
         <v>223</v>
       </c>
       <c r="E103" t="s">
-        <v>661</v>
+        <v>703</v>
       </c>
       <c r="F103" t="s">
-        <v>43</v>
+        <v>704</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B104" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="C104" t="s">
         <v>259</v>
@@ -7194,895 +7275,895 @@
         <v>223</v>
       </c>
       <c r="E104" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="F104" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="B105" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C105" t="s">
-        <v>264</v>
+        <v>353</v>
       </c>
       <c r="D105" t="s">
         <v>223</v>
       </c>
       <c r="E105" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F105" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B106" t="s">
-        <v>560</v>
+        <v>714</v>
       </c>
       <c r="C106" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D106" t="s">
         <v>223</v>
       </c>
       <c r="E106" t="s">
-        <v>561</v>
+        <v>715</v>
       </c>
       <c r="F106" t="s">
-        <v>562</v>
+        <v>716</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>718</v>
+      </c>
+      <c r="B107" t="s">
+        <v>719</v>
+      </c>
+      <c r="C107" t="s">
+        <v>640</v>
+      </c>
+      <c r="D107" t="s">
+        <v>223</v>
+      </c>
+      <c r="E107" t="s">
+        <v>720</v>
+      </c>
+      <c r="F107" t="s">
+        <v>721</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="B107" t="s">
-        <v>560</v>
-      </c>
-      <c r="C107" t="s">
-        <v>264</v>
-      </c>
-      <c r="D107" t="s">
-        <v>223</v>
-      </c>
-      <c r="E107" t="s">
-        <v>561</v>
-      </c>
-      <c r="F107" t="s">
-        <v>562</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>723</v>
+      </c>
+      <c r="B108" t="s">
         <v>724</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>725</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>223</v>
+      </c>
+      <c r="E108" t="s">
+        <v>670</v>
+      </c>
+      <c r="F108" t="s">
+        <v>43</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D108" t="s">
-        <v>223</v>
-      </c>
-      <c r="E108" t="s">
-        <v>727</v>
-      </c>
-      <c r="F108" t="s">
-        <v>341</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>727</v>
+      </c>
+      <c r="B109" t="s">
+        <v>728</v>
+      </c>
+      <c r="C109" t="s">
+        <v>259</v>
+      </c>
+      <c r="D109" t="s">
+        <v>223</v>
+      </c>
+      <c r="E109" t="s">
         <v>729</v>
       </c>
-      <c r="B109" t="s">
-        <v>263</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="F109" t="s">
         <v>730</v>
       </c>
-      <c r="D109" t="s">
-        <v>223</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="H109" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="F109" t="s">
-        <v>43</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>732</v>
+      </c>
+      <c r="B110" t="s">
         <v>733</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
+        <v>264</v>
+      </c>
+      <c r="D110" t="s">
+        <v>223</v>
+      </c>
+      <c r="E110" t="s">
         <v>734</v>
       </c>
-      <c r="C110" t="s">
-        <v>254</v>
-      </c>
-      <c r="D110" t="s">
-        <v>452</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>735</v>
       </c>
-      <c r="F110" t="s">
+      <c r="H110" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>737</v>
+      </c>
+      <c r="B111" t="s">
+        <v>560</v>
+      </c>
+      <c r="C111" t="s">
+        <v>264</v>
+      </c>
+      <c r="D111" t="s">
+        <v>223</v>
+      </c>
+      <c r="E111" t="s">
+        <v>561</v>
+      </c>
+      <c r="F111" t="s">
+        <v>562</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="B111" t="s">
-        <v>739</v>
-      </c>
-      <c r="C111" t="s">
-        <v>210</v>
-      </c>
-      <c r="D111" t="s">
-        <v>223</v>
-      </c>
-      <c r="E111" t="s">
-        <v>740</v>
-      </c>
-      <c r="F111" t="s">
-        <v>43</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B112" t="s">
-        <v>743</v>
+        <v>560</v>
       </c>
       <c r="C112" t="s">
-        <v>744</v>
+        <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="E112" t="s">
-        <v>745</v>
+        <v>561</v>
       </c>
       <c r="F112" t="s">
-        <v>746</v>
+        <v>562</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B113" t="s">
-        <v>749</v>
+        <v>560</v>
       </c>
       <c r="C113" t="s">
-        <v>750</v>
+        <v>264</v>
       </c>
       <c r="D113" t="s">
         <v>223</v>
       </c>
       <c r="E113" t="s">
-        <v>751</v>
+        <v>561</v>
       </c>
       <c r="F113" t="s">
-        <v>43</v>
+        <v>562</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>744</v>
       </c>
       <c r="C114" t="s">
-        <v>247</v>
+        <v>745</v>
       </c>
       <c r="D114" t="s">
         <v>223</v>
       </c>
       <c r="E114" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="F114" t="s">
-        <v>43</v>
+        <v>341</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B115" t="s">
-        <v>757</v>
+        <v>263</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>749</v>
       </c>
       <c r="D115" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="E115" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="F115" t="s">
-        <v>759</v>
+        <v>43</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="B116" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="C116" t="s">
-        <v>431</v>
+        <v>254</v>
       </c>
       <c r="D116" t="s">
-        <v>289</v>
+        <v>452</v>
       </c>
       <c r="E116" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="F116" t="s">
-        <v>420</v>
+        <v>755</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="B117" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="C117" t="s">
-        <v>325</v>
+        <v>210</v>
       </c>
       <c r="D117" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="E117" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="F117" t="s">
-        <v>768</v>
+        <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="B118" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="C118" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="D118" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="E118" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="F118" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="B119" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="C119" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="D119" t="s">
         <v>223</v>
       </c>
       <c r="E119" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="F119" t="s">
-        <v>780</v>
+        <v>43</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="B120" t="s">
-        <v>783</v>
+        <v>246</v>
       </c>
       <c r="C120" t="s">
-        <v>784</v>
+        <v>247</v>
       </c>
       <c r="D120" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="E120" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="F120" t="s">
-        <v>786</v>
+        <v>43</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="B121" t="s">
-        <v>674</v>
+        <v>776</v>
       </c>
       <c r="C121" t="s">
         <v>259</v>
       </c>
       <c r="D121" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="E121" t="s">
-        <v>675</v>
+        <v>777</v>
       </c>
       <c r="F121" t="s">
-        <v>676</v>
+        <v>778</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="B122" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="C122" t="s">
-        <v>210</v>
+        <v>431</v>
       </c>
       <c r="D122" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="E122" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="F122" t="s">
-        <v>626</v>
+        <v>420</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="B123" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C123" t="s">
-        <v>796</v>
+        <v>325</v>
       </c>
       <c r="D123" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="E123" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="F123" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="B124" t="s">
-        <v>483</v>
+        <v>790</v>
       </c>
       <c r="C124" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="D124" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="E124" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="F124" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B125" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C125" t="s">
-        <v>210</v>
+        <v>797</v>
       </c>
       <c r="D125" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="E125" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="F125" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="B126" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="C126" t="s">
-        <v>264</v>
+        <v>803</v>
       </c>
       <c r="D126" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="E126" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="F126" t="s">
-        <v>626</v>
+        <v>805</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B127" t="s">
-        <v>300</v>
+        <v>687</v>
       </c>
       <c r="C127" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="E127" t="s">
-        <v>303</v>
+        <v>688</v>
       </c>
       <c r="F127" t="s">
-        <v>43</v>
+        <v>689</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="B128" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C128" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="D128" t="s">
         <v>223</v>
       </c>
       <c r="E128" t="s">
-        <v>635</v>
+        <v>811</v>
       </c>
       <c r="F128" t="s">
-        <v>817</v>
+        <v>632</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="B129" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="C129" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="D129" t="s">
         <v>223</v>
       </c>
       <c r="E129" t="s">
-        <v>43</v>
+        <v>816</v>
       </c>
       <c r="F129" t="s">
-        <v>768</v>
+        <v>817</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>819</v>
+      </c>
+      <c r="B130" t="s">
+        <v>483</v>
+      </c>
+      <c r="C130" t="s">
+        <v>820</v>
+      </c>
+      <c r="D130" t="s">
+        <v>302</v>
+      </c>
+      <c r="E130" t="s">
+        <v>821</v>
+      </c>
+      <c r="F130" t="s">
+        <v>822</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="B130" t="s">
-        <v>824</v>
-      </c>
-      <c r="C130" t="s">
-        <v>825</v>
-      </c>
-      <c r="D130" t="s">
-        <v>223</v>
-      </c>
-      <c r="E130" t="s">
-        <v>826</v>
-      </c>
-      <c r="F130" t="s">
-        <v>43</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>824</v>
+      </c>
+      <c r="B131" t="s">
+        <v>825</v>
+      </c>
+      <c r="C131" t="s">
+        <v>210</v>
+      </c>
+      <c r="D131" t="s">
+        <v>289</v>
+      </c>
+      <c r="E131" t="s">
+        <v>826</v>
+      </c>
+      <c r="F131" t="s">
+        <v>827</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="B131" t="s">
-        <v>829</v>
-      </c>
-      <c r="C131" t="s">
-        <v>830</v>
-      </c>
-      <c r="D131" t="s">
-        <v>223</v>
-      </c>
-      <c r="E131" t="s">
-        <v>831</v>
-      </c>
-      <c r="F131" t="s">
-        <v>43</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B132" t="s">
-        <v>234</v>
+        <v>810</v>
       </c>
       <c r="C132" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="D132" t="s">
         <v>223</v>
       </c>
       <c r="E132" t="s">
-        <v>378</v>
+        <v>830</v>
       </c>
       <c r="F132" t="s">
-        <v>236</v>
+        <v>632</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B133" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="C133" t="s">
-        <v>210</v>
+        <v>301</v>
       </c>
       <c r="D133" t="s">
         <v>223</v>
       </c>
       <c r="E133" t="s">
-        <v>836</v>
+        <v>303</v>
       </c>
       <c r="F133" t="s">
         <v>43</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B134" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C134" t="s">
-        <v>840</v>
+        <v>259</v>
       </c>
       <c r="D134" t="s">
         <v>223</v>
       </c>
       <c r="E134" t="s">
-        <v>841</v>
+        <v>641</v>
       </c>
       <c r="F134" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="B135" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C135" t="s">
-        <v>210</v>
+        <v>840</v>
       </c>
       <c r="D135" t="s">
         <v>223</v>
       </c>
       <c r="E135" t="s">
-        <v>846</v>
+        <v>43</v>
       </c>
       <c r="F135" t="s">
-        <v>847</v>
+        <v>787</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="B136" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>844</v>
       </c>
       <c r="D136" t="s">
         <v>223</v>
       </c>
       <c r="E136" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="F136" t="s">
-        <v>852</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="B137" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="C137" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="D137" t="s">
         <v>223</v>
       </c>
       <c r="E137" t="s">
-        <v>661</v>
+        <v>850</v>
       </c>
       <c r="F137" t="s">
-        <v>857</v>
+        <v>43</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="B138" t="s">
-        <v>860</v>
+        <v>234</v>
       </c>
       <c r="C138" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="E138" t="s">
-        <v>861</v>
+        <v>378</v>
       </c>
       <c r="F138" t="s">
-        <v>525</v>
+        <v>236</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="B139" t="s">
-        <v>864</v>
+        <v>234</v>
       </c>
       <c r="C139" t="s">
-        <v>865</v>
+        <v>210</v>
       </c>
       <c r="D139" t="s">
         <v>223</v>
       </c>
       <c r="E139" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="F139" t="s">
-        <v>746</v>
+        <v>43</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="B140" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="C140" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="D140" t="s">
         <v>223</v>
       </c>
       <c r="E140" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="F140" t="s">
-        <v>613</v>
+        <v>861</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="B141" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="D141" t="s">
         <v>223</v>
       </c>
       <c r="E141" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="F141" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="B142" t="s">
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="C142" t="s">
-        <v>264</v>
+        <v>869</v>
       </c>
       <c r="D142" t="s">
         <v>223</v>
       </c>
       <c r="E142" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="F142" t="s">
-        <v>562</v>
+        <v>623</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B143" t="s">
-        <v>294</v>
+        <v>873</v>
       </c>
       <c r="C143" t="s">
         <v>259</v>
@@ -8091,197 +8172,381 @@
         <v>223</v>
       </c>
       <c r="E143" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="F143" t="s">
-        <v>43</v>
+        <v>875</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B144" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C144" t="s">
-        <v>750</v>
+        <v>879</v>
       </c>
       <c r="D144" t="s">
         <v>223</v>
       </c>
       <c r="E144" t="s">
-        <v>886</v>
+        <v>670</v>
       </c>
       <c r="F144" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>882</v>
+      </c>
+      <c r="B145" t="s">
+        <v>883</v>
+      </c>
+      <c r="C145" t="s">
+        <v>264</v>
+      </c>
+      <c r="D145" t="s">
+        <v>289</v>
+      </c>
+      <c r="E145" t="s">
         <v>884</v>
       </c>
-      <c r="B145" t="s">
-        <v>889</v>
-      </c>
-      <c r="C145" t="s">
-        <v>210</v>
-      </c>
-      <c r="D145" t="s">
-        <v>223</v>
-      </c>
-      <c r="E145" t="s">
-        <v>890</v>
-      </c>
       <c r="F145" t="s">
-        <v>891</v>
+        <v>525</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="B146" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="C146" t="s">
-        <v>247</v>
+        <v>888</v>
       </c>
       <c r="D146" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="E146" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="F146" t="s">
-        <v>896</v>
+        <v>765</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="B147" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="C147" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="D147" t="s">
         <v>223</v>
       </c>
       <c r="E147" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="F147" t="s">
-        <v>902</v>
+        <v>613</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="B148" t="s">
-        <v>697</v>
+        <v>897</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D148" t="s">
         <v>223</v>
       </c>
       <c r="E148" t="s">
-        <v>698</v>
+        <v>898</v>
       </c>
       <c r="F148" t="s">
-        <v>699</v>
+        <v>899</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B149" t="s">
-        <v>907</v>
+        <v>560</v>
       </c>
       <c r="C149" t="s">
-        <v>353</v>
+        <v>264</v>
       </c>
       <c r="D149" t="s">
         <v>223</v>
       </c>
       <c r="E149" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="F149" t="s">
-        <v>43</v>
+        <v>562</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="B150" t="s">
-        <v>911</v>
+        <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>912</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
         <v>223</v>
       </c>
       <c r="E150" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="F150" t="s">
-        <v>914</v>
+        <v>43</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>907</v>
+      </c>
+      <c r="B151" t="s">
+        <v>908</v>
+      </c>
+      <c r="C151" t="s">
+        <v>769</v>
+      </c>
+      <c r="D151" t="s">
+        <v>223</v>
+      </c>
+      <c r="E151" t="s">
+        <v>909</v>
+      </c>
+      <c r="F151" t="s">
+        <v>910</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>907</v>
+      </c>
+      <c r="B152" t="s">
+        <v>912</v>
+      </c>
+      <c r="C152" t="s">
+        <v>210</v>
+      </c>
+      <c r="D152" t="s">
+        <v>223</v>
+      </c>
+      <c r="E152" t="s">
+        <v>913</v>
+      </c>
+      <c r="F152" t="s">
+        <v>914</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>916</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B153" t="s">
         <v>917</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C153" t="s">
+        <v>247</v>
+      </c>
+      <c r="D153" t="s">
+        <v>302</v>
+      </c>
+      <c r="E153" t="s">
+        <v>918</v>
+      </c>
+      <c r="F153" t="s">
+        <v>919</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>921</v>
+      </c>
+      <c r="B154" t="s">
+        <v>922</v>
+      </c>
+      <c r="C154" t="s">
+        <v>923</v>
+      </c>
+      <c r="D154" t="s">
+        <v>223</v>
+      </c>
+      <c r="E154" t="s">
+        <v>924</v>
+      </c>
+      <c r="F154" t="s">
+        <v>925</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>927</v>
+      </c>
+      <c r="B155" t="s">
+        <v>714</v>
+      </c>
+      <c r="C155" t="s">
+        <v>269</v>
+      </c>
+      <c r="D155" t="s">
+        <v>223</v>
+      </c>
+      <c r="E155" t="s">
+        <v>715</v>
+      </c>
+      <c r="F155" t="s">
+        <v>716</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>929</v>
+      </c>
+      <c r="B156" t="s">
+        <v>620</v>
+      </c>
+      <c r="C156" t="s">
+        <v>930</v>
+      </c>
+      <c r="D156" t="s">
+        <v>223</v>
+      </c>
+      <c r="E156" t="s">
+        <v>931</v>
+      </c>
+      <c r="F156" t="s">
+        <v>623</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>933</v>
+      </c>
+      <c r="B157" t="s">
+        <v>934</v>
+      </c>
+      <c r="C157" t="s">
+        <v>353</v>
+      </c>
+      <c r="D157" t="s">
+        <v>223</v>
+      </c>
+      <c r="E157" t="s">
+        <v>935</v>
+      </c>
+      <c r="F157" t="s">
+        <v>43</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>937</v>
+      </c>
+      <c r="B158" t="s">
+        <v>938</v>
+      </c>
+      <c r="C158" t="s">
+        <v>939</v>
+      </c>
+      <c r="D158" t="s">
+        <v>223</v>
+      </c>
+      <c r="E158" t="s">
+        <v>940</v>
+      </c>
+      <c r="F158" t="s">
+        <v>941</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>943</v>
+      </c>
+      <c r="B159" t="s">
+        <v>944</v>
+      </c>
+      <c r="C159" t="s">
         <v>17</v>
       </c>
-      <c r="D151" t="s">
-        <v>223</v>
-      </c>
-      <c r="E151" t="s">
-        <v>918</v>
-      </c>
-      <c r="F151" t="s">
-        <v>919</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>920</v>
+      <c r="D159" t="s">
+        <v>223</v>
+      </c>
+      <c r="E159" t="s">
+        <v>945</v>
+      </c>
+      <c r="F159" t="s">
+        <v>946</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>947</v>
       </c>
     </row>
   </sheetData>
@@ -8437,6 +8702,14 @@
     <hyperlink ref="H149" r:id="rId148"/>
     <hyperlink ref="H150" r:id="rId149"/>
     <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -8486,13 +8759,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="B2" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="C2" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="D2" t="s">
         <v>43</v>
@@ -8501,21 +8774,21 @@
         <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
       <c r="B3" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="C3" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="D3" t="s">
         <v>43</v>
@@ -8524,21 +8797,21 @@
         <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="B4" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="C4" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D4" t="s">
         <v>43</v>
@@ -8547,21 +8820,21 @@
         <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="B5" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="C5" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="D5" t="s">
         <v>43</v>
@@ -8570,21 +8843,21 @@
         <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="B6" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="C6" t="s">
-        <v>942</v>
+        <v>969</v>
       </c>
       <c r="D6" t="s">
         <v>43</v>
@@ -8593,21 +8866,21 @@
         <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
       <c r="B7" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="C7" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -8616,21 +8889,21 @@
         <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="B8" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="C8" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="D8" t="s">
         <v>43</v>
@@ -8639,21 +8912,21 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="B9" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="C9" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
@@ -8662,21 +8935,21 @@
         <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="B10" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="C10" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
       <c r="D10" t="s">
         <v>43</v>
@@ -8685,21 +8958,21 @@
         <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="B11" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="C11" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -8708,21 +8981,21 @@
         <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="B12" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="C12" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -8731,21 +9004,21 @@
         <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="B13" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="C13" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>
@@ -8754,21 +9027,21 @@
         <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="B14" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
       <c r="C14" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -8777,21 +9050,21 @@
         <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
       <c r="B15" t="s">
-        <v>979</v>
+        <v>1006</v>
       </c>
       <c r="C15" t="s">
-        <v>980</v>
+        <v>1007</v>
       </c>
       <c r="D15" t="s">
         <v>43</v>
@@ -8800,21 +9073,21 @@
         <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
       <c r="B16" t="s">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="C16" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D16" t="s">
         <v>43</v>
@@ -8823,21 +9096,21 @@
         <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
       <c r="B17" t="s">
-        <v>986</v>
+        <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>987</v>
+        <v>1014</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -8846,21 +9119,21 @@
         <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>988</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
       <c r="B18" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D18" t="s">
         <v>43</v>
@@ -8869,21 +9142,21 @@
         <v>43</v>
       </c>
       <c r="F18" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>992</v>
+        <v>1019</v>
       </c>
       <c r="B19" t="s">
-        <v>993</v>
+        <v>1020</v>
       </c>
       <c r="C19" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
       <c r="D19" t="s">
         <v>43</v>
@@ -8892,21 +9165,21 @@
         <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="B20" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
       <c r="C20" t="s">
-        <v>998</v>
+        <v>1025</v>
       </c>
       <c r="D20" t="s">
         <v>43</v>
@@ -8915,21 +9188,21 @@
         <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
       <c r="B21" t="s">
-        <v>1001</v>
+        <v>1028</v>
       </c>
       <c r="C21" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
@@ -8938,21 +9211,21 @@
         <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>1002</v>
+        <v>1029</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1003</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="B22" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
       <c r="C22" t="s">
-        <v>1006</v>
+        <v>1033</v>
       </c>
       <c r="D22" t="s">
         <v>43</v>
@@ -8964,18 +9237,18 @@
         <v>579</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1007</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1008</v>
+        <v>1035</v>
       </c>
       <c r="B23" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="C23" t="s">
-        <v>1010</v>
+        <v>1037</v>
       </c>
       <c r="D23" t="s">
         <v>43</v>
@@ -8984,21 +9257,21 @@
         <v>43</v>
       </c>
       <c r="F23" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1011</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1012</v>
+        <v>1039</v>
       </c>
       <c r="B24" t="s">
-        <v>1013</v>
+        <v>1040</v>
       </c>
       <c r="C24" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -9007,21 +9280,21 @@
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1015</v>
+        <v>1042</v>
       </c>
       <c r="B25" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="C25" t="s">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="D25" t="s">
         <v>43</v>
@@ -9030,18 +9303,18 @@
         <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1018</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
       <c r="B26" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
       <c r="C26" t="s">
         <v>388</v>
@@ -9053,21 +9326,21 @@
         <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1021</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="B27" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
       <c r="C27" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="D27" t="s">
         <v>43</v>
@@ -9076,21 +9349,21 @@
         <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1026</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="B28" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="C28" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="D28" t="s">
         <v>43</v>
@@ -9099,21 +9372,21 @@
         <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1030</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1031</v>
+        <v>1058</v>
       </c>
       <c r="B29" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
       <c r="C29" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="D29" t="s">
         <v>43</v>
@@ -9122,21 +9395,21 @@
         <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="B30" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
       <c r="C30" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
       <c r="D30" t="s">
         <v>43</v>
@@ -9145,21 +9418,21 @@
         <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
       <c r="B31" t="s">
-        <v>1040</v>
+        <v>1067</v>
       </c>
       <c r="C31" t="s">
-        <v>1041</v>
+        <v>1068</v>
       </c>
       <c r="D31" t="s">
         <v>43</v>
@@ -9168,21 +9441,21 @@
         <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1042</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1043</v>
+        <v>1070</v>
       </c>
       <c r="B32" t="s">
-        <v>1044</v>
+        <v>1071</v>
       </c>
       <c r="C32" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
       <c r="D32" t="s">
         <v>43</v>
@@ -9191,21 +9464,21 @@
         <v>43</v>
       </c>
       <c r="F32" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1046</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
       <c r="B33" t="s">
-        <v>1048</v>
+        <v>1075</v>
       </c>
       <c r="C33" t="s">
-        <v>1049</v>
+        <v>1076</v>
       </c>
       <c r="D33" t="s">
         <v>43</v>
@@ -9214,21 +9487,21 @@
         <v>43</v>
       </c>
       <c r="F33" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1050</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1051</v>
+        <v>1078</v>
       </c>
       <c r="B34" t="s">
-        <v>1052</v>
+        <v>1079</v>
       </c>
       <c r="C34" t="s">
-        <v>1053</v>
+        <v>1080</v>
       </c>
       <c r="D34" t="s">
         <v>43</v>
@@ -9237,21 +9510,21 @@
         <v>43</v>
       </c>
       <c r="F34" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1054</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1055</v>
+        <v>1082</v>
       </c>
       <c r="B35" t="s">
-        <v>1056</v>
+        <v>1083</v>
       </c>
       <c r="C35" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D35" t="s">
         <v>43</v>
@@ -9260,18 +9533,18 @@
         <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1057</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="B36" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
       <c r="C36" t="s">
         <v>264</v>
@@ -9283,21 +9556,21 @@
         <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1060</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1061</v>
+        <v>1088</v>
       </c>
       <c r="B37" t="s">
-        <v>1062</v>
+        <v>1089</v>
       </c>
       <c r="C37" t="s">
-        <v>1063</v>
+        <v>1090</v>
       </c>
       <c r="D37" t="s">
         <v>43</v>
@@ -9306,21 +9579,21 @@
         <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1064</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1065</v>
+        <v>1092</v>
       </c>
       <c r="B38" t="s">
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="C38" t="s">
-        <v>1067</v>
+        <v>1094</v>
       </c>
       <c r="D38" t="s">
         <v>43</v>
@@ -9329,21 +9602,21 @@
         <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1068</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1069</v>
+        <v>1096</v>
       </c>
       <c r="B39" t="s">
-        <v>1070</v>
+        <v>1097</v>
       </c>
       <c r="C39" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D39" t="s">
         <v>43</v>
@@ -9352,21 +9625,21 @@
         <v>43</v>
       </c>
       <c r="F39" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>1071</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1072</v>
+        <v>1099</v>
       </c>
       <c r="B40" t="s">
-        <v>1073</v>
+        <v>1100</v>
       </c>
       <c r="C40" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="D40" t="s">
         <v>43</v>
@@ -9375,21 +9648,21 @@
         <v>43</v>
       </c>
       <c r="F40" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="B41" t="s">
-        <v>1077</v>
+        <v>1104</v>
       </c>
       <c r="C41" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D41" t="s">
         <v>43</v>
@@ -9398,21 +9671,21 @@
         <v>43</v>
       </c>
       <c r="F41" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1079</v>
+        <v>1106</v>
       </c>
       <c r="B42" t="s">
-        <v>1080</v>
+        <v>1107</v>
       </c>
       <c r="C42" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="D42" t="s">
         <v>43</v>
@@ -9421,21 +9694,21 @@
         <v>43</v>
       </c>
       <c r="F42" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1083</v>
+        <v>1110</v>
       </c>
       <c r="B43" t="s">
-        <v>1084</v>
+        <v>1111</v>
       </c>
       <c r="C43" t="s">
-        <v>1049</v>
+        <v>1076</v>
       </c>
       <c r="D43" t="s">
         <v>43</v>
@@ -9444,21 +9717,21 @@
         <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1085</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1086</v>
+        <v>1113</v>
       </c>
       <c r="B44" t="s">
-        <v>1087</v>
+        <v>1114</v>
       </c>
       <c r="C44" t="s">
-        <v>1088</v>
+        <v>1115</v>
       </c>
       <c r="D44" t="s">
         <v>43</v>
@@ -9467,21 +9740,21 @@
         <v>43</v>
       </c>
       <c r="F44" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1089</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1090</v>
+        <v>1117</v>
       </c>
       <c r="B45" t="s">
-        <v>1091</v>
+        <v>1118</v>
       </c>
       <c r="C45" t="s">
-        <v>1092</v>
+        <v>1119</v>
       </c>
       <c r="D45" t="s">
         <v>43</v>
@@ -9490,21 +9763,21 @@
         <v>43</v>
       </c>
       <c r="F45" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1093</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1094</v>
+        <v>1121</v>
       </c>
       <c r="B46" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="C46" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="D46" t="s">
         <v>43</v>
@@ -9513,21 +9786,21 @@
         <v>43</v>
       </c>
       <c r="F46" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1095</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1096</v>
+        <v>1123</v>
       </c>
       <c r="B47" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="C47" t="s">
-        <v>1098</v>
+        <v>1125</v>
       </c>
       <c r="D47" t="s">
         <v>43</v>
@@ -9536,21 +9809,21 @@
         <v>43</v>
       </c>
       <c r="F47" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1100</v>
+        <v>1127</v>
       </c>
       <c r="B48" t="s">
-        <v>1101</v>
+        <v>1128</v>
       </c>
       <c r="C48" t="s">
-        <v>1098</v>
+        <v>1125</v>
       </c>
       <c r="D48" t="s">
         <v>43</v>
@@ -9559,21 +9832,21 @@
         <v>43</v>
       </c>
       <c r="F48" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1102</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1103</v>
+        <v>1130</v>
       </c>
       <c r="B49" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="C49" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="D49" t="s">
         <v>43</v>
@@ -9582,21 +9855,21 @@
         <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1104</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1105</v>
+        <v>1132</v>
       </c>
       <c r="B50" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C50" t="s">
-        <v>1107</v>
+        <v>1134</v>
       </c>
       <c r="D50" t="s">
         <v>43</v>
@@ -9605,18 +9878,18 @@
         <v>43</v>
       </c>
       <c r="F50" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1108</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1109</v>
+        <v>1136</v>
       </c>
       <c r="B51" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="C51" t="s">
         <v>388</v>
@@ -9628,21 +9901,21 @@
         <v>43</v>
       </c>
       <c r="F51" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1111</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1112</v>
+        <v>1139</v>
       </c>
       <c r="B52" t="s">
-        <v>1113</v>
+        <v>1140</v>
       </c>
       <c r="C52" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="D52" t="s">
         <v>43</v>
@@ -9651,21 +9924,21 @@
         <v>43</v>
       </c>
       <c r="F52" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1116</v>
+        <v>1143</v>
       </c>
       <c r="B53" t="s">
-        <v>1117</v>
+        <v>1144</v>
       </c>
       <c r="C53" t="s">
-        <v>1118</v>
+        <v>1145</v>
       </c>
       <c r="D53" t="s">
         <v>43</v>
@@ -9674,10 +9947,10 @@
         <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1119</v>
+        <v>1146</v>
       </c>
     </row>
   </sheetData>

--- a/docs/xlsx/jobs-2026-08-18.xlsx
+++ b/docs/xlsx/jobs-2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1149">
   <si>
     <t>Title</t>
   </si>
@@ -2195,6 +2195,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/6288a4a770c44f9e9af00e6ad8930882-marketing-and-communications-associate-the-ark-inc-chicago</t>
+  </si>
+  <si>
+    <t>The Ark</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6288a4a770c44f9e9af00e6ad8930882-marketing-and-communications-associate-the-ark-chicago</t>
   </si>
   <si>
     <t>MCH Data Analyst</t>
@@ -4876,7 +4882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -7378,56 +7384,56 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>723</v>
+      </c>
+      <c r="B109" t="s">
         <v>727</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
+        <v>725</v>
+      </c>
+      <c r="D109" t="s">
+        <v>223</v>
+      </c>
+      <c r="E109" t="s">
+        <v>670</v>
+      </c>
+      <c r="F109" t="s">
+        <v>43</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="C109" t="s">
-        <v>259</v>
-      </c>
-      <c r="D109" t="s">
-        <v>223</v>
-      </c>
-      <c r="E109" t="s">
-        <v>729</v>
-      </c>
-      <c r="F109" t="s">
-        <v>730</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>729</v>
+      </c>
+      <c r="B110" t="s">
+        <v>730</v>
+      </c>
+      <c r="C110" t="s">
+        <v>259</v>
+      </c>
+      <c r="D110" t="s">
+        <v>223</v>
+      </c>
+      <c r="E110" t="s">
+        <v>731</v>
+      </c>
+      <c r="F110" t="s">
         <v>732</v>
       </c>
-      <c r="B110" t="s">
+      <c r="H110" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="C110" t="s">
-        <v>264</v>
-      </c>
-      <c r="D110" t="s">
-        <v>223</v>
-      </c>
-      <c r="E110" t="s">
-        <v>734</v>
-      </c>
-      <c r="F110" t="s">
-        <v>735</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B111" t="s">
-        <v>560</v>
+        <v>735</v>
       </c>
       <c r="C111" t="s">
         <v>264</v>
@@ -7436,10 +7442,10 @@
         <v>223</v>
       </c>
       <c r="E111" t="s">
-        <v>561</v>
+        <v>736</v>
       </c>
       <c r="F111" t="s">
-        <v>562</v>
+        <v>737</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>738</v>
@@ -7496,318 +7502,318 @@
         <v>743</v>
       </c>
       <c r="B114" t="s">
+        <v>560</v>
+      </c>
+      <c r="C114" t="s">
+        <v>264</v>
+      </c>
+      <c r="D114" t="s">
+        <v>223</v>
+      </c>
+      <c r="E114" t="s">
+        <v>561</v>
+      </c>
+      <c r="F114" t="s">
+        <v>562</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="C114" t="s">
-        <v>745</v>
-      </c>
-      <c r="D114" t="s">
-        <v>223</v>
-      </c>
-      <c r="E114" t="s">
-        <v>746</v>
-      </c>
-      <c r="F114" t="s">
-        <v>341</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>745</v>
+      </c>
+      <c r="B115" t="s">
+        <v>746</v>
+      </c>
+      <c r="C115" t="s">
+        <v>747</v>
+      </c>
+      <c r="D115" t="s">
+        <v>223</v>
+      </c>
+      <c r="E115" t="s">
         <v>748</v>
       </c>
-      <c r="B115" t="s">
-        <v>263</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="F115" t="s">
+        <v>341</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="D115" t="s">
-        <v>223</v>
-      </c>
-      <c r="E115" t="s">
-        <v>750</v>
-      </c>
-      <c r="F115" t="s">
-        <v>43</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>750</v>
+      </c>
+      <c r="B116" t="s">
+        <v>263</v>
+      </c>
+      <c r="C116" t="s">
+        <v>751</v>
+      </c>
+      <c r="D116" t="s">
+        <v>223</v>
+      </c>
+      <c r="E116" t="s">
         <v>752</v>
       </c>
-      <c r="B116" t="s">
+      <c r="F116" t="s">
+        <v>43</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="C116" t="s">
-        <v>254</v>
-      </c>
-      <c r="D116" t="s">
-        <v>452</v>
-      </c>
-      <c r="E116" t="s">
-        <v>754</v>
-      </c>
-      <c r="F116" t="s">
-        <v>755</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>754</v>
+      </c>
+      <c r="B117" t="s">
+        <v>755</v>
+      </c>
+      <c r="C117" t="s">
+        <v>254</v>
+      </c>
+      <c r="D117" t="s">
+        <v>452</v>
+      </c>
+      <c r="E117" t="s">
+        <v>756</v>
+      </c>
+      <c r="F117" t="s">
         <v>757</v>
       </c>
-      <c r="B117" t="s">
+      <c r="H117" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="C117" t="s">
-        <v>210</v>
-      </c>
-      <c r="D117" t="s">
-        <v>223</v>
-      </c>
-      <c r="E117" t="s">
-        <v>759</v>
-      </c>
-      <c r="F117" t="s">
-        <v>43</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>759</v>
+      </c>
+      <c r="B118" t="s">
+        <v>760</v>
+      </c>
+      <c r="C118" t="s">
+        <v>210</v>
+      </c>
+      <c r="D118" t="s">
+        <v>223</v>
+      </c>
+      <c r="E118" t="s">
         <v>761</v>
       </c>
-      <c r="B118" t="s">
+      <c r="F118" t="s">
+        <v>43</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="C118" t="s">
-        <v>763</v>
-      </c>
-      <c r="D118" t="s">
-        <v>289</v>
-      </c>
-      <c r="E118" t="s">
-        <v>764</v>
-      </c>
-      <c r="F118" t="s">
-        <v>765</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>763</v>
+      </c>
+      <c r="B119" t="s">
+        <v>764</v>
+      </c>
+      <c r="C119" t="s">
+        <v>765</v>
+      </c>
+      <c r="D119" t="s">
+        <v>289</v>
+      </c>
+      <c r="E119" t="s">
+        <v>766</v>
+      </c>
+      <c r="F119" t="s">
         <v>767</v>
       </c>
-      <c r="B119" t="s">
+      <c r="H119" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="C119" t="s">
-        <v>769</v>
-      </c>
-      <c r="D119" t="s">
-        <v>223</v>
-      </c>
-      <c r="E119" t="s">
-        <v>770</v>
-      </c>
-      <c r="F119" t="s">
-        <v>43</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>769</v>
+      </c>
+      <c r="B120" t="s">
+        <v>770</v>
+      </c>
+      <c r="C120" t="s">
+        <v>771</v>
+      </c>
+      <c r="D120" t="s">
+        <v>223</v>
+      </c>
+      <c r="E120" t="s">
         <v>772</v>
       </c>
-      <c r="B120" t="s">
-        <v>246</v>
-      </c>
-      <c r="C120" t="s">
-        <v>247</v>
-      </c>
-      <c r="D120" t="s">
-        <v>223</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
+        <v>43</v>
+      </c>
+      <c r="H120" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="F120" t="s">
-        <v>43</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>774</v>
+      </c>
+      <c r="B121" t="s">
+        <v>246</v>
+      </c>
+      <c r="C121" t="s">
+        <v>247</v>
+      </c>
+      <c r="D121" t="s">
+        <v>223</v>
+      </c>
+      <c r="E121" t="s">
         <v>775</v>
       </c>
-      <c r="B121" t="s">
+      <c r="F121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="C121" t="s">
-        <v>259</v>
-      </c>
-      <c r="D121" t="s">
-        <v>289</v>
-      </c>
-      <c r="E121" t="s">
-        <v>777</v>
-      </c>
-      <c r="F121" t="s">
-        <v>778</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B122" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C122" t="s">
-        <v>431</v>
+        <v>259</v>
       </c>
       <c r="D122" t="s">
         <v>289</v>
       </c>
       <c r="E122" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F122" t="s">
-        <v>420</v>
+        <v>780</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B123" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C123" t="s">
-        <v>325</v>
+        <v>431</v>
       </c>
       <c r="D123" t="s">
         <v>289</v>
       </c>
       <c r="E123" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="F123" t="s">
-        <v>787</v>
+        <v>420</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>786</v>
+      </c>
+      <c r="B124" t="s">
+        <v>787</v>
+      </c>
+      <c r="C124" t="s">
+        <v>325</v>
+      </c>
+      <c r="D124" t="s">
+        <v>289</v>
+      </c>
+      <c r="E124" t="s">
+        <v>788</v>
+      </c>
+      <c r="F124" t="s">
         <v>789</v>
       </c>
-      <c r="B124" t="s">
+      <c r="H124" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="C124" t="s">
-        <v>791</v>
-      </c>
-      <c r="D124" t="s">
-        <v>223</v>
-      </c>
-      <c r="E124" t="s">
-        <v>792</v>
-      </c>
-      <c r="F124" t="s">
-        <v>793</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>791</v>
+      </c>
+      <c r="B125" t="s">
+        <v>792</v>
+      </c>
+      <c r="C125" t="s">
+        <v>793</v>
+      </c>
+      <c r="D125" t="s">
+        <v>223</v>
+      </c>
+      <c r="E125" t="s">
+        <v>794</v>
+      </c>
+      <c r="F125" t="s">
         <v>795</v>
       </c>
-      <c r="B125" t="s">
+      <c r="H125" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="C125" t="s">
-        <v>797</v>
-      </c>
-      <c r="D125" t="s">
-        <v>223</v>
-      </c>
-      <c r="E125" t="s">
-        <v>798</v>
-      </c>
-      <c r="F125" t="s">
-        <v>799</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>797</v>
+      </c>
+      <c r="B126" t="s">
+        <v>798</v>
+      </c>
+      <c r="C126" t="s">
+        <v>799</v>
+      </c>
+      <c r="D126" t="s">
+        <v>223</v>
+      </c>
+      <c r="E126" t="s">
+        <v>800</v>
+      </c>
+      <c r="F126" t="s">
         <v>801</v>
       </c>
-      <c r="B126" t="s">
+      <c r="H126" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="C126" t="s">
-        <v>803</v>
-      </c>
-      <c r="D126" t="s">
-        <v>302</v>
-      </c>
-      <c r="E126" t="s">
-        <v>804</v>
-      </c>
-      <c r="F126" t="s">
-        <v>805</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B127" t="s">
-        <v>687</v>
+        <v>804</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>805</v>
       </c>
       <c r="D127" t="s">
         <v>302</v>
       </c>
       <c r="E127" t="s">
-        <v>688</v>
+        <v>806</v>
       </c>
       <c r="F127" t="s">
-        <v>689</v>
+        <v>807</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>808</v>
@@ -7818,134 +7824,134 @@
         <v>809</v>
       </c>
       <c r="B128" t="s">
+        <v>687</v>
+      </c>
+      <c r="C128" t="s">
+        <v>259</v>
+      </c>
+      <c r="D128" t="s">
+        <v>302</v>
+      </c>
+      <c r="E128" t="s">
+        <v>688</v>
+      </c>
+      <c r="F128" t="s">
+        <v>689</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="C128" t="s">
-        <v>210</v>
-      </c>
-      <c r="D128" t="s">
-        <v>223</v>
-      </c>
-      <c r="E128" t="s">
-        <v>811</v>
-      </c>
-      <c r="F128" t="s">
-        <v>632</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>811</v>
+      </c>
+      <c r="B129" t="s">
+        <v>812</v>
+      </c>
+      <c r="C129" t="s">
+        <v>210</v>
+      </c>
+      <c r="D129" t="s">
+        <v>223</v>
+      </c>
+      <c r="E129" t="s">
         <v>813</v>
       </c>
-      <c r="B129" t="s">
+      <c r="F129" t="s">
+        <v>632</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="C129" t="s">
-        <v>815</v>
-      </c>
-      <c r="D129" t="s">
-        <v>223</v>
-      </c>
-      <c r="E129" t="s">
-        <v>816</v>
-      </c>
-      <c r="F129" t="s">
-        <v>817</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>815</v>
+      </c>
+      <c r="B130" t="s">
+        <v>816</v>
+      </c>
+      <c r="C130" t="s">
+        <v>817</v>
+      </c>
+      <c r="D130" t="s">
+        <v>223</v>
+      </c>
+      <c r="E130" t="s">
+        <v>818</v>
+      </c>
+      <c r="F130" t="s">
         <v>819</v>
       </c>
-      <c r="B130" t="s">
-        <v>483</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="H130" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="D130" t="s">
-        <v>302</v>
-      </c>
-      <c r="E130" t="s">
-        <v>821</v>
-      </c>
-      <c r="F130" t="s">
-        <v>822</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>821</v>
+      </c>
+      <c r="B131" t="s">
+        <v>483</v>
+      </c>
+      <c r="C131" t="s">
+        <v>822</v>
+      </c>
+      <c r="D131" t="s">
+        <v>302</v>
+      </c>
+      <c r="E131" t="s">
+        <v>823</v>
+      </c>
+      <c r="F131" t="s">
         <v>824</v>
       </c>
-      <c r="B131" t="s">
+      <c r="H131" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="C131" t="s">
-        <v>210</v>
-      </c>
-      <c r="D131" t="s">
-        <v>289</v>
-      </c>
-      <c r="E131" t="s">
-        <v>826</v>
-      </c>
-      <c r="F131" t="s">
-        <v>827</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>826</v>
+      </c>
+      <c r="B132" t="s">
+        <v>827</v>
+      </c>
+      <c r="C132" t="s">
+        <v>210</v>
+      </c>
+      <c r="D132" t="s">
+        <v>289</v>
+      </c>
+      <c r="E132" t="s">
+        <v>828</v>
+      </c>
+      <c r="F132" t="s">
         <v>829</v>
       </c>
-      <c r="B132" t="s">
-        <v>810</v>
-      </c>
-      <c r="C132" t="s">
-        <v>264</v>
-      </c>
-      <c r="D132" t="s">
-        <v>223</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="H132" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="F132" t="s">
-        <v>632</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>831</v>
+      </c>
+      <c r="B133" t="s">
+        <v>812</v>
+      </c>
+      <c r="C133" t="s">
+        <v>264</v>
+      </c>
+      <c r="D133" t="s">
+        <v>223</v>
+      </c>
+      <c r="E133" t="s">
         <v>832</v>
       </c>
-      <c r="B133" t="s">
-        <v>300</v>
-      </c>
-      <c r="C133" t="s">
-        <v>301</v>
-      </c>
-      <c r="D133" t="s">
-        <v>223</v>
-      </c>
-      <c r="E133" t="s">
-        <v>303</v>
-      </c>
       <c r="F133" t="s">
-        <v>43</v>
+        <v>632</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>833</v>
@@ -7956,111 +7962,111 @@
         <v>834</v>
       </c>
       <c r="B134" t="s">
+        <v>300</v>
+      </c>
+      <c r="C134" t="s">
+        <v>301</v>
+      </c>
+      <c r="D134" t="s">
+        <v>223</v>
+      </c>
+      <c r="E134" t="s">
+        <v>303</v>
+      </c>
+      <c r="F134" t="s">
+        <v>43</v>
+      </c>
+      <c r="H134" s="2" t="s">
         <v>835</v>
-      </c>
-      <c r="C134" t="s">
-        <v>259</v>
-      </c>
-      <c r="D134" t="s">
-        <v>223</v>
-      </c>
-      <c r="E134" t="s">
-        <v>641</v>
-      </c>
-      <c r="F134" t="s">
-        <v>836</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>836</v>
+      </c>
+      <c r="B135" t="s">
+        <v>837</v>
+      </c>
+      <c r="C135" t="s">
+        <v>259</v>
+      </c>
+      <c r="D135" t="s">
+        <v>223</v>
+      </c>
+      <c r="E135" t="s">
+        <v>641</v>
+      </c>
+      <c r="F135" t="s">
         <v>838</v>
       </c>
-      <c r="B135" t="s">
+      <c r="H135" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="C135" t="s">
-        <v>840</v>
-      </c>
-      <c r="D135" t="s">
-        <v>223</v>
-      </c>
-      <c r="E135" t="s">
-        <v>43</v>
-      </c>
-      <c r="F135" t="s">
-        <v>787</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>840</v>
+      </c>
+      <c r="B136" t="s">
+        <v>841</v>
+      </c>
+      <c r="C136" t="s">
         <v>842</v>
       </c>
-      <c r="B136" t="s">
+      <c r="D136" t="s">
+        <v>223</v>
+      </c>
+      <c r="E136" t="s">
+        <v>43</v>
+      </c>
+      <c r="F136" t="s">
+        <v>789</v>
+      </c>
+      <c r="H136" s="2" t="s">
         <v>843</v>
-      </c>
-      <c r="C136" t="s">
-        <v>844</v>
-      </c>
-      <c r="D136" t="s">
-        <v>223</v>
-      </c>
-      <c r="E136" t="s">
-        <v>845</v>
-      </c>
-      <c r="F136" t="s">
-        <v>43</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>844</v>
+      </c>
+      <c r="B137" t="s">
+        <v>845</v>
+      </c>
+      <c r="C137" t="s">
+        <v>846</v>
+      </c>
+      <c r="D137" t="s">
+        <v>223</v>
+      </c>
+      <c r="E137" t="s">
         <v>847</v>
       </c>
-      <c r="B137" t="s">
+      <c r="F137" t="s">
+        <v>43</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="C137" t="s">
-        <v>849</v>
-      </c>
-      <c r="D137" t="s">
-        <v>223</v>
-      </c>
-      <c r="E137" t="s">
-        <v>850</v>
-      </c>
-      <c r="F137" t="s">
-        <v>43</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>849</v>
+      </c>
+      <c r="B138" t="s">
+        <v>850</v>
+      </c>
+      <c r="C138" t="s">
+        <v>851</v>
+      </c>
+      <c r="D138" t="s">
+        <v>223</v>
+      </c>
+      <c r="E138" t="s">
         <v>852</v>
       </c>
-      <c r="B138" t="s">
-        <v>234</v>
-      </c>
-      <c r="C138" t="s">
-        <v>210</v>
-      </c>
-      <c r="D138" t="s">
-        <v>223</v>
-      </c>
-      <c r="E138" t="s">
-        <v>378</v>
-      </c>
       <c r="F138" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>853</v>
@@ -8080,228 +8086,228 @@
         <v>223</v>
       </c>
       <c r="E139" t="s">
+        <v>378</v>
+      </c>
+      <c r="F139" t="s">
+        <v>236</v>
+      </c>
+      <c r="H139" s="2" t="s">
         <v>855</v>
-      </c>
-      <c r="F139" t="s">
-        <v>43</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>856</v>
+      </c>
+      <c r="B140" t="s">
+        <v>234</v>
+      </c>
+      <c r="C140" t="s">
+        <v>210</v>
+      </c>
+      <c r="D140" t="s">
+        <v>223</v>
+      </c>
+      <c r="E140" t="s">
         <v>857</v>
       </c>
-      <c r="B140" t="s">
+      <c r="F140" t="s">
+        <v>43</v>
+      </c>
+      <c r="H140" s="2" t="s">
         <v>858</v>
-      </c>
-      <c r="C140" t="s">
-        <v>859</v>
-      </c>
-      <c r="D140" t="s">
-        <v>223</v>
-      </c>
-      <c r="E140" t="s">
-        <v>860</v>
-      </c>
-      <c r="F140" t="s">
-        <v>861</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>859</v>
+      </c>
+      <c r="B141" t="s">
+        <v>860</v>
+      </c>
+      <c r="C141" t="s">
+        <v>861</v>
+      </c>
+      <c r="D141" t="s">
+        <v>223</v>
+      </c>
+      <c r="E141" t="s">
+        <v>862</v>
+      </c>
+      <c r="F141" t="s">
         <v>863</v>
       </c>
-      <c r="B141" t="s">
+      <c r="H141" s="2" t="s">
         <v>864</v>
-      </c>
-      <c r="C141" t="s">
-        <v>210</v>
-      </c>
-      <c r="D141" t="s">
-        <v>223</v>
-      </c>
-      <c r="E141" t="s">
-        <v>865</v>
-      </c>
-      <c r="F141" t="s">
-        <v>866</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>865</v>
+      </c>
+      <c r="B142" t="s">
+        <v>866</v>
+      </c>
+      <c r="C142" t="s">
+        <v>210</v>
+      </c>
+      <c r="D142" t="s">
+        <v>223</v>
+      </c>
+      <c r="E142" t="s">
+        <v>867</v>
+      </c>
+      <c r="F142" t="s">
         <v>868</v>
       </c>
-      <c r="B142" t="s">
-        <v>620</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="H142" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="D142" t="s">
-        <v>223</v>
-      </c>
-      <c r="E142" t="s">
-        <v>870</v>
-      </c>
-      <c r="F142" t="s">
-        <v>623</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>870</v>
+      </c>
+      <c r="B143" t="s">
+        <v>620</v>
+      </c>
+      <c r="C143" t="s">
+        <v>871</v>
+      </c>
+      <c r="D143" t="s">
+        <v>223</v>
+      </c>
+      <c r="E143" t="s">
         <v>872</v>
       </c>
-      <c r="B143" t="s">
+      <c r="F143" t="s">
+        <v>623</v>
+      </c>
+      <c r="H143" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="C143" t="s">
-        <v>259</v>
-      </c>
-      <c r="D143" t="s">
-        <v>223</v>
-      </c>
-      <c r="E143" t="s">
-        <v>874</v>
-      </c>
-      <c r="F143" t="s">
-        <v>875</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>874</v>
+      </c>
+      <c r="B144" t="s">
+        <v>875</v>
+      </c>
+      <c r="C144" t="s">
+        <v>259</v>
+      </c>
+      <c r="D144" t="s">
+        <v>223</v>
+      </c>
+      <c r="E144" t="s">
+        <v>876</v>
+      </c>
+      <c r="F144" t="s">
         <v>877</v>
       </c>
-      <c r="B144" t="s">
+      <c r="H144" s="2" t="s">
         <v>878</v>
-      </c>
-      <c r="C144" t="s">
-        <v>879</v>
-      </c>
-      <c r="D144" t="s">
-        <v>223</v>
-      </c>
-      <c r="E144" t="s">
-        <v>670</v>
-      </c>
-      <c r="F144" t="s">
-        <v>880</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>879</v>
+      </c>
+      <c r="B145" t="s">
+        <v>880</v>
+      </c>
+      <c r="C145" t="s">
+        <v>881</v>
+      </c>
+      <c r="D145" t="s">
+        <v>223</v>
+      </c>
+      <c r="E145" t="s">
+        <v>670</v>
+      </c>
+      <c r="F145" t="s">
         <v>882</v>
       </c>
-      <c r="B145" t="s">
+      <c r="H145" s="2" t="s">
         <v>883</v>
-      </c>
-      <c r="C145" t="s">
-        <v>264</v>
-      </c>
-      <c r="D145" t="s">
-        <v>289</v>
-      </c>
-      <c r="E145" t="s">
-        <v>884</v>
-      </c>
-      <c r="F145" t="s">
-        <v>525</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>884</v>
+      </c>
+      <c r="B146" t="s">
+        <v>885</v>
+      </c>
+      <c r="C146" t="s">
+        <v>264</v>
+      </c>
+      <c r="D146" t="s">
+        <v>289</v>
+      </c>
+      <c r="E146" t="s">
         <v>886</v>
       </c>
-      <c r="B146" t="s">
+      <c r="F146" t="s">
+        <v>525</v>
+      </c>
+      <c r="H146" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="C146" t="s">
-        <v>888</v>
-      </c>
-      <c r="D146" t="s">
-        <v>223</v>
-      </c>
-      <c r="E146" t="s">
-        <v>889</v>
-      </c>
-      <c r="F146" t="s">
-        <v>765</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>888</v>
+      </c>
+      <c r="B147" t="s">
+        <v>889</v>
+      </c>
+      <c r="C147" t="s">
+        <v>890</v>
+      </c>
+      <c r="D147" t="s">
+        <v>223</v>
+      </c>
+      <c r="E147" t="s">
         <v>891</v>
       </c>
-      <c r="B147" t="s">
+      <c r="F147" t="s">
+        <v>767</v>
+      </c>
+      <c r="H147" s="2" t="s">
         <v>892</v>
-      </c>
-      <c r="C147" t="s">
-        <v>893</v>
-      </c>
-      <c r="D147" t="s">
-        <v>223</v>
-      </c>
-      <c r="E147" t="s">
-        <v>894</v>
-      </c>
-      <c r="F147" t="s">
-        <v>613</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>893</v>
+      </c>
+      <c r="B148" t="s">
+        <v>894</v>
+      </c>
+      <c r="C148" t="s">
+        <v>895</v>
+      </c>
+      <c r="D148" t="s">
+        <v>223</v>
+      </c>
+      <c r="E148" t="s">
         <v>896</v>
       </c>
-      <c r="B148" t="s">
+      <c r="F148" t="s">
+        <v>613</v>
+      </c>
+      <c r="H148" s="2" t="s">
         <v>897</v>
-      </c>
-      <c r="C148" t="s">
-        <v>264</v>
-      </c>
-      <c r="D148" t="s">
-        <v>223</v>
-      </c>
-      <c r="E148" t="s">
-        <v>898</v>
-      </c>
-      <c r="F148" t="s">
-        <v>899</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B149" t="s">
-        <v>560</v>
+        <v>899</v>
       </c>
       <c r="C149" t="s">
         <v>264</v>
@@ -8310,148 +8316,148 @@
         <v>223</v>
       </c>
       <c r="E149" t="s">
+        <v>900</v>
+      </c>
+      <c r="F149" t="s">
+        <v>901</v>
+      </c>
+      <c r="H149" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="F149" t="s">
-        <v>562</v>
-      </c>
-      <c r="H149" s="2" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>903</v>
+      </c>
+      <c r="B150" t="s">
+        <v>560</v>
+      </c>
+      <c r="C150" t="s">
+        <v>264</v>
+      </c>
+      <c r="D150" t="s">
+        <v>223</v>
+      </c>
+      <c r="E150" t="s">
         <v>904</v>
       </c>
-      <c r="B150" t="s">
-        <v>294</v>
-      </c>
-      <c r="C150" t="s">
-        <v>259</v>
-      </c>
-      <c r="D150" t="s">
-        <v>223</v>
-      </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
+        <v>562</v>
+      </c>
+      <c r="H150" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="F150" t="s">
-        <v>43</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>906</v>
+      </c>
+      <c r="B151" t="s">
+        <v>294</v>
+      </c>
+      <c r="C151" t="s">
+        <v>259</v>
+      </c>
+      <c r="D151" t="s">
+        <v>223</v>
+      </c>
+      <c r="E151" t="s">
         <v>907</v>
       </c>
-      <c r="B151" t="s">
+      <c r="F151" t="s">
+        <v>43</v>
+      </c>
+      <c r="H151" s="2" t="s">
         <v>908</v>
-      </c>
-      <c r="C151" t="s">
-        <v>769</v>
-      </c>
-      <c r="D151" t="s">
-        <v>223</v>
-      </c>
-      <c r="E151" t="s">
-        <v>909</v>
-      </c>
-      <c r="F151" t="s">
-        <v>910</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B152" t="s">
+        <v>910</v>
+      </c>
+      <c r="C152" t="s">
+        <v>771</v>
+      </c>
+      <c r="D152" t="s">
+        <v>223</v>
+      </c>
+      <c r="E152" t="s">
+        <v>911</v>
+      </c>
+      <c r="F152" t="s">
         <v>912</v>
       </c>
-      <c r="C152" t="s">
-        <v>210</v>
-      </c>
-      <c r="D152" t="s">
-        <v>223</v>
-      </c>
-      <c r="E152" t="s">
+      <c r="H152" s="2" t="s">
         <v>913</v>
-      </c>
-      <c r="F152" t="s">
-        <v>914</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>909</v>
+      </c>
+      <c r="B153" t="s">
+        <v>914</v>
+      </c>
+      <c r="C153" t="s">
+        <v>210</v>
+      </c>
+      <c r="D153" t="s">
+        <v>223</v>
+      </c>
+      <c r="E153" t="s">
+        <v>915</v>
+      </c>
+      <c r="F153" t="s">
         <v>916</v>
       </c>
-      <c r="B153" t="s">
+      <c r="H153" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="C153" t="s">
-        <v>247</v>
-      </c>
-      <c r="D153" t="s">
-        <v>302</v>
-      </c>
-      <c r="E153" t="s">
-        <v>918</v>
-      </c>
-      <c r="F153" t="s">
-        <v>919</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>918</v>
+      </c>
+      <c r="B154" t="s">
+        <v>919</v>
+      </c>
+      <c r="C154" t="s">
+        <v>247</v>
+      </c>
+      <c r="D154" t="s">
+        <v>302</v>
+      </c>
+      <c r="E154" t="s">
+        <v>920</v>
+      </c>
+      <c r="F154" t="s">
         <v>921</v>
       </c>
-      <c r="B154" t="s">
+      <c r="H154" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="C154" t="s">
-        <v>923</v>
-      </c>
-      <c r="D154" t="s">
-        <v>223</v>
-      </c>
-      <c r="E154" t="s">
-        <v>924</v>
-      </c>
-      <c r="F154" t="s">
-        <v>925</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>923</v>
+      </c>
+      <c r="B155" t="s">
+        <v>924</v>
+      </c>
+      <c r="C155" t="s">
+        <v>925</v>
+      </c>
+      <c r="D155" t="s">
+        <v>223</v>
+      </c>
+      <c r="E155" t="s">
+        <v>926</v>
+      </c>
+      <c r="F155" t="s">
         <v>927</v>
-      </c>
-      <c r="B155" t="s">
-        <v>714</v>
-      </c>
-      <c r="C155" t="s">
-        <v>269</v>
-      </c>
-      <c r="D155" t="s">
-        <v>223</v>
-      </c>
-      <c r="E155" t="s">
-        <v>715</v>
-      </c>
-      <c r="F155" t="s">
-        <v>716</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>928</v>
@@ -8462,91 +8468,114 @@
         <v>929</v>
       </c>
       <c r="B156" t="s">
-        <v>620</v>
+        <v>714</v>
       </c>
       <c r="C156" t="s">
+        <v>269</v>
+      </c>
+      <c r="D156" t="s">
+        <v>223</v>
+      </c>
+      <c r="E156" t="s">
+        <v>715</v>
+      </c>
+      <c r="F156" t="s">
+        <v>716</v>
+      </c>
+      <c r="H156" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="D156" t="s">
-        <v>223</v>
-      </c>
-      <c r="E156" t="s">
-        <v>931</v>
-      </c>
-      <c r="F156" t="s">
-        <v>623</v>
-      </c>
-      <c r="H156" s="2" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>931</v>
+      </c>
+      <c r="B157" t="s">
+        <v>620</v>
+      </c>
+      <c r="C157" t="s">
+        <v>932</v>
+      </c>
+      <c r="D157" t="s">
+        <v>223</v>
+      </c>
+      <c r="E157" t="s">
         <v>933</v>
       </c>
-      <c r="B157" t="s">
+      <c r="F157" t="s">
+        <v>623</v>
+      </c>
+      <c r="H157" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="C157" t="s">
-        <v>353</v>
-      </c>
-      <c r="D157" t="s">
-        <v>223</v>
-      </c>
-      <c r="E157" t="s">
-        <v>935</v>
-      </c>
-      <c r="F157" t="s">
-        <v>43</v>
-      </c>
-      <c r="H157" s="2" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>935</v>
+      </c>
+      <c r="B158" t="s">
+        <v>936</v>
+      </c>
+      <c r="C158" t="s">
+        <v>353</v>
+      </c>
+      <c r="D158" t="s">
+        <v>223</v>
+      </c>
+      <c r="E158" t="s">
         <v>937</v>
       </c>
-      <c r="B158" t="s">
+      <c r="F158" t="s">
+        <v>43</v>
+      </c>
+      <c r="H158" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="C158" t="s">
-        <v>939</v>
-      </c>
-      <c r="D158" t="s">
-        <v>223</v>
-      </c>
-      <c r="E158" t="s">
-        <v>940</v>
-      </c>
-      <c r="F158" t="s">
-        <v>941</v>
-      </c>
-      <c r="H158" s="2" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>939</v>
+      </c>
+      <c r="B159" t="s">
+        <v>940</v>
+      </c>
+      <c r="C159" t="s">
+        <v>941</v>
+      </c>
+      <c r="D159" t="s">
+        <v>223</v>
+      </c>
+      <c r="E159" t="s">
+        <v>942</v>
+      </c>
+      <c r="F159" t="s">
         <v>943</v>
       </c>
-      <c r="B159" t="s">
+      <c r="H159" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="C159" t="s">
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>945</v>
+      </c>
+      <c r="B160" t="s">
+        <v>946</v>
+      </c>
+      <c r="C160" t="s">
         <v>17</v>
       </c>
-      <c r="D159" t="s">
-        <v>223</v>
-      </c>
-      <c r="E159" t="s">
-        <v>945</v>
-      </c>
-      <c r="F159" t="s">
-        <v>946</v>
-      </c>
-      <c r="H159" s="2" t="s">
+      <c r="D160" t="s">
+        <v>223</v>
+      </c>
+      <c r="E160" t="s">
         <v>947</v>
+      </c>
+      <c r="F160" t="s">
+        <v>948</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -8710,6 +8739,7 @@
     <hyperlink ref="H157" r:id="rId156"/>
     <hyperlink ref="H158" r:id="rId157"/>
     <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -8759,13 +8789,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D2" t="s">
         <v>43</v>
@@ -8774,21 +8804,21 @@
         <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D3" t="s">
         <v>43</v>
@@ -8797,21 +8827,21 @@
         <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B4" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C4" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D4" t="s">
         <v>43</v>
@@ -8820,21 +8850,21 @@
         <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B5" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C5" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D5" t="s">
         <v>43</v>
@@ -8843,21 +8873,21 @@
         <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B6" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C6" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D6" t="s">
         <v>43</v>
@@ -8866,21 +8896,21 @@
         <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B7" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C7" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -8889,21 +8919,21 @@
         <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B8" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C8" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D8" t="s">
         <v>43</v>
@@ -8912,21 +8942,21 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B9" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C9" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
@@ -8935,21 +8965,21 @@
         <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B10" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C10" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D10" t="s">
         <v>43</v>
@@ -8958,21 +8988,21 @@
         <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B11" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C11" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -8981,21 +9011,21 @@
         <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B12" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C12" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -9004,21 +9034,21 @@
         <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B13" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C13" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>
@@ -9027,21 +9057,21 @@
         <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B14" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C14" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -9050,21 +9080,21 @@
         <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B15" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C15" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D15" t="s">
         <v>43</v>
@@ -9073,21 +9103,21 @@
         <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B16" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D16" t="s">
         <v>43</v>
@@ -9096,21 +9126,21 @@
         <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B17" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C17" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -9119,21 +9149,21 @@
         <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B18" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C18" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D18" t="s">
         <v>43</v>
@@ -9142,21 +9172,21 @@
         <v>43</v>
       </c>
       <c r="F18" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B19" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C19" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D19" t="s">
         <v>43</v>
@@ -9165,21 +9195,21 @@
         <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B20" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C20" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D20" t="s">
         <v>43</v>
@@ -9188,21 +9218,21 @@
         <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B21" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C21" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
@@ -9211,21 +9241,21 @@
         <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B22" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C22" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D22" t="s">
         <v>43</v>
@@ -9237,18 +9267,18 @@
         <v>579</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B23" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C23" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D23" t="s">
         <v>43</v>
@@ -9257,21 +9287,21 @@
         <v>43</v>
       </c>
       <c r="F23" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B24" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C24" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -9280,21 +9310,21 @@
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B25" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C25" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D25" t="s">
         <v>43</v>
@@ -9303,18 +9333,18 @@
         <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B26" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C26" t="s">
         <v>388</v>
@@ -9326,21 +9356,21 @@
         <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B27" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C27" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D27" t="s">
         <v>43</v>
@@ -9349,21 +9379,21 @@
         <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B28" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C28" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D28" t="s">
         <v>43</v>
@@ -9372,21 +9402,21 @@
         <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B29" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C29" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D29" t="s">
         <v>43</v>
@@ -9395,21 +9425,21 @@
         <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B30" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C30" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D30" t="s">
         <v>43</v>
@@ -9418,21 +9448,21 @@
         <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B31" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C31" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D31" t="s">
         <v>43</v>
@@ -9441,21 +9471,21 @@
         <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B32" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C32" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D32" t="s">
         <v>43</v>
@@ -9464,21 +9494,21 @@
         <v>43</v>
       </c>
       <c r="F32" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B33" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C33" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D33" t="s">
         <v>43</v>
@@ -9487,21 +9517,21 @@
         <v>43</v>
       </c>
       <c r="F33" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B34" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C34" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D34" t="s">
         <v>43</v>
@@ -9510,21 +9540,21 @@
         <v>43</v>
       </c>
       <c r="F34" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B35" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C35" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D35" t="s">
         <v>43</v>
@@ -9533,18 +9563,18 @@
         <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B36" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C36" t="s">
         <v>264</v>
@@ -9556,21 +9586,21 @@
         <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B37" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C37" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D37" t="s">
         <v>43</v>
@@ -9579,21 +9609,21 @@
         <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B38" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C38" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D38" t="s">
         <v>43</v>
@@ -9602,21 +9632,21 @@
         <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B39" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C39" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D39" t="s">
         <v>43</v>
@@ -9625,21 +9655,21 @@
         <v>43</v>
       </c>
       <c r="F39" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B40" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C40" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D40" t="s">
         <v>43</v>
@@ -9648,21 +9678,21 @@
         <v>43</v>
       </c>
       <c r="F40" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B41" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C41" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D41" t="s">
         <v>43</v>
@@ -9671,21 +9701,21 @@
         <v>43</v>
       </c>
       <c r="F41" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B42" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C42" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D42" t="s">
         <v>43</v>
@@ -9694,21 +9724,21 @@
         <v>43</v>
       </c>
       <c r="F42" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B43" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C43" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D43" t="s">
         <v>43</v>
@@ -9717,21 +9747,21 @@
         <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B44" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C44" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="D44" t="s">
         <v>43</v>
@@ -9740,21 +9770,21 @@
         <v>43</v>
       </c>
       <c r="F44" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B45" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C45" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D45" t="s">
         <v>43</v>
@@ -9763,21 +9793,21 @@
         <v>43</v>
       </c>
       <c r="F45" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B46" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C46" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D46" t="s">
         <v>43</v>
@@ -9786,21 +9816,21 @@
         <v>43</v>
       </c>
       <c r="F46" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B47" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C47" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D47" t="s">
         <v>43</v>
@@ -9809,22 +9839,22 @@
         <v>43</v>
       </c>
       <c r="F47" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C48" t="s">
         <v>1127</v>
       </c>
-      <c r="B48" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1125</v>
-      </c>
       <c r="D48" t="s">
         <v>43</v>
       </c>
@@ -9832,21 +9862,21 @@
         <v>43</v>
       </c>
       <c r="F48" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B49" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C49" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D49" t="s">
         <v>43</v>
@@ -9855,21 +9885,21 @@
         <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B50" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C50" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D50" t="s">
         <v>43</v>
@@ -9878,18 +9908,18 @@
         <v>43</v>
       </c>
       <c r="F50" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B51" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C51" t="s">
         <v>388</v>
@@ -9901,21 +9931,21 @@
         <v>43</v>
       </c>
       <c r="F51" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B52" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C52" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D52" t="s">
         <v>43</v>
@@ -9924,21 +9954,21 @@
         <v>43</v>
       </c>
       <c r="F52" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B53" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C53" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D53" t="s">
         <v>43</v>
@@ -9947,10 +9977,10 @@
         <v>43</v>
       </c>
       <c r="F53" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
   </sheetData>
